--- a/apps/scenario_explorer/dev/mapping_overview.xlsx
+++ b/apps/scenario_explorer/dev/mapping_overview.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12315" uniqueCount="2937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12527" uniqueCount="2980">
   <si>
     <t>Key</t>
   </si>
@@ -7207,46 +7207,46 @@
     <t>Final Energy|Industry|Non-Metallic Minerals|Cement|w/ CCS|Solids|Coke</t>
   </si>
   <si>
-    <t>direct air capture (solvent, gas heat) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, gas heat) with storage (gases energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, industrial steam heat) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, industrial steam heat) with storage (heat energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, heat pump) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, heat pump) with storage (electricity energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, hydrogen heat) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent, hydrogen heat) with storage (hydrogen energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (solvent) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (sorbent, heat pump) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (sorbent, heat pump) with storage (electricity energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (sorbent, gas heat) with storage</t>
-  </si>
-  <si>
-    <t>direct air capture (sorbent, gas heat) with storage (gases energy use)</t>
-  </si>
-  <si>
-    <t>direct air capture (sorbent) with storage</t>
+    <t>direct air capture (solvent, high-temp, gas heat) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, gas heat) with storage (gases energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, industrial steam heat) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, industrial steam heat) with storage (heat energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, heat pump) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, heat pump) with storage (electricity energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, hydrogen heat) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp, hydrogen heat) with storage (hydrogen energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (solvent, high-temp) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (sorbent, low-temp, heat pump) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (sorbent, low-temp, heat pump) with storage (electricity energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (sorbent, low-temp, gas heat) with storage</t>
+  </si>
+  <si>
+    <t>direct air capture (sorbent, low-temp, gas heat) with storage (gases energy use)</t>
+  </si>
+  <si>
+    <t>direct air capture (sorbent, low-temp) with storage</t>
   </si>
   <si>
     <t>enhanced rock weathering</t>
@@ -7327,24 +7327,24 @@
     <t>Carbon Sequestration|Direct Air Capture|Solvent</t>
   </si>
   <si>
+    <t>Final Energy|Carbon Management|Direct Air Capture|Solvent|Electricity|PV</t>
+  </si>
+  <si>
+    <t>Final Energy|Carbon Management|Direct Air Capture|Solvent|Electricity|CSP</t>
+  </si>
+  <si>
+    <t>Carbon Sequestration|Direct Air Capture|Sorbent</t>
+  </si>
+  <si>
+    <t>Carbon Capture|Direct Air Capture|Sorbent</t>
+  </si>
+  <si>
+    <t>Carbon Removal|Geological Storage|Direct Air Capture|Solid Sorbent</t>
+  </si>
+  <si>
     <t>Secondary Energy|Consumption|Direct Air Capture|Electricity</t>
   </si>
   <si>
-    <t>Final Energy|Carbon Management|Direct Air Capture|Solvent|Electricity|PV</t>
-  </si>
-  <si>
-    <t>Final Energy|Carbon Management|Direct Air Capture|Solvent|Electricity|CSP</t>
-  </si>
-  <si>
-    <t>Carbon Sequestration|Direct Air Capture|Sorbent</t>
-  </si>
-  <si>
-    <t>Carbon Capture|Direct Air Capture|Sorbent</t>
-  </si>
-  <si>
-    <t>Carbon Removal|Geological Storage|Direct Air Capture|Solid Sorbent</t>
-  </si>
-  <si>
     <t>Final Energy|Carbon Management|Direct Air Capture|Sorbent|Electricity|CSP</t>
   </si>
   <si>
@@ -7615,18 +7615,6 @@
     <t>Final Energy|Transport|Pass|Road|Bus|BEV</t>
   </si>
   <si>
-    <t>heat, from natural gas</t>
-  </si>
-  <si>
-    <t>heat, from light fuel oil</t>
-  </si>
-  <si>
-    <t>heat, from wood chips</t>
-  </si>
-  <si>
-    <t>heat, from coal furnace</t>
-  </si>
-  <si>
     <t>heat, buildings, from district heating</t>
   </si>
   <si>
@@ -7636,7 +7624,7 @@
     <t>heat, buildings, from hydrogen fuel cell</t>
   </si>
   <si>
-    <t>heat, buildings, from natural gas</t>
+    <t>heat, buildings, from natural gas boiler</t>
   </si>
   <si>
     <t>heat, buildings, from biomethane boiler</t>
@@ -7669,28 +7657,31 @@
     <t>heat, buildings, from light fuel oil boiler</t>
   </si>
   <si>
-    <t>heat, industrial, from hydrogen</t>
-  </si>
-  <si>
-    <t>heat, industrial, from hydrogen conversion</t>
-  </si>
-  <si>
-    <t>heat, industrial, from electric heater</t>
+    <t>heat, buildings, residual</t>
+  </si>
+  <si>
+    <t>heat, industrial, from biomass boiler</t>
+  </si>
+  <si>
+    <t>heat, industrial, from hydrogen boiler</t>
+  </si>
+  <si>
+    <t>heat, industrial, from hydrogen fuel cell</t>
+  </si>
+  <si>
+    <t>heat, industrial, from electric boiler</t>
   </si>
   <si>
     <t>heat, industrial, from heat pump</t>
   </si>
   <si>
-    <t>heat, industrial, from natural gas CHP</t>
-  </si>
-  <si>
-    <t>heat, industrial, from biogas CHP</t>
-  </si>
-  <si>
-    <t>heat, industrial, from coal CHP</t>
-  </si>
-  <si>
-    <t>heat, industrial, from biomass CHP</t>
+    <t>heat, industrial, from natural gas boiler</t>
+  </si>
+  <si>
+    <t>heat, industrial, from biomethane boiler</t>
+  </si>
+  <si>
+    <t>heat, industrial, from coal furnace</t>
   </si>
   <si>
     <t>heat, industrial, from light fuel oil boiler</t>
@@ -7699,118 +7690,256 @@
     <t>heat, industrial, from biofuel boiler</t>
   </si>
   <si>
-    <t>heat, industrial, from geothermal</t>
-  </si>
-  <si>
     <t>heat, industrial, from solar thermal</t>
   </si>
   <si>
     <t>heat, industrial, from district heating</t>
   </si>
   <si>
+    <t>heat, secondary, from biomass</t>
+  </si>
+  <si>
+    <t>heat, secondary, from biomass CHP</t>
+  </si>
+  <si>
+    <t>heat, secondary, from biomass residual</t>
+  </si>
+  <si>
+    <t>heat, secondary, from biomass with CCS</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coal</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coal CHP</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coal residual</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coal with CCS</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coke</t>
+  </si>
+  <si>
+    <t>heat, secondary, from coke with CCS</t>
+  </si>
+  <si>
+    <t>heat, secondary, from natural gas</t>
+  </si>
+  <si>
+    <t>heat, secondary, from natural gas CHP</t>
+  </si>
+  <si>
+    <t>heat, secondary, from natural gas residual</t>
+  </si>
+  <si>
+    <t>heat, secondary, from natural gas with CCS</t>
+  </si>
+  <si>
+    <t>heat, secondary, from oil</t>
+  </si>
+  <si>
+    <t>heat, secondary, from oil with CCS</t>
+  </si>
+  <si>
+    <t>heat, secondary, from electricity</t>
+  </si>
+  <si>
+    <t>heat, secondary, from heat pump</t>
+  </si>
+  <si>
+    <t>heat, secondary, from geothermal</t>
+  </si>
+  <si>
+    <t>heat, secondary, from nuclear</t>
+  </si>
+  <si>
+    <t>heat, secondary, from solar thermal</t>
+  </si>
+  <si>
+    <t>heat, secondary, residual</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|District Heat</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Hydrogen</t>
+  </si>
+  <si>
+    <t>Final Energy|Residential and Commercial|Hydrogen|Combustion</t>
+  </si>
+  <si>
+    <t>Final Energy|Residential and Commercial|Hydrogen|Fuel Cell</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Gas</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Coal</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Biomass</t>
+  </si>
+  <si>
+    <t>Final Energy|Residential and Commercial|Electricity|Thermal|Heat Pumps</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Electricity</t>
+  </si>
+  <si>
+    <t>Final Energy|Residential and Commercial|Electricity|Thermal|Resistance</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Buildings|Oil</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Biomass</t>
+  </si>
+  <si>
+    <t>FE|Industry|Solids|+|Biomass</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Hydrogen</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Hydrogen|Combustion</t>
+  </si>
+  <si>
+    <t>FE|Industry|+|Hydrogen</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Hydrogen|Fuel Cells</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Electricity|Thermal|Resistance</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Electricity|Thermal|Heat Pumps</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Gas</t>
+  </si>
+  <si>
+    <t>FE|Industry|Gases|+|Fossil</t>
+  </si>
+  <si>
+    <t>FE|Industry|Gases|+|Biomass</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Coal</t>
+  </si>
+  <si>
+    <t>FE|Industry|Solids|+|Fossil</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Oil</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Liquids|Oil|Thermal</t>
+  </si>
+  <si>
+    <t>FE|Industry|Liquids|+|Fossil</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Liquids|Biomass|Thermal</t>
+  </si>
+  <si>
+    <t>FE|Industry|Liquids|+|Biomass</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|Solar</t>
+  </si>
+  <si>
+    <t>Final Energy|Industry|Other Sector|Solar</t>
+  </si>
+  <si>
+    <t>Final Energy|Heat|Industry|District Heat</t>
+  </si>
+  <si>
+    <t>FE|Industry|+|Heat</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Biomass</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Biomass|Heat|w/o CCS</t>
+  </si>
+  <si>
+    <t>SE|Heat|Biomass|+|Combined Heat and Power</t>
+  </si>
+  <si>
+    <t>{'terms': [{'variable': 'SE|Heat|+|Biomass'}, {'variable': 'SE|Heat|Biomass|+|Combined Heat and Power', 'coefficient': -1}]}</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Biomass|Heat|w CCS</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Coal</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Coal|Heat|w/o CCS</t>
+  </si>
+  <si>
+    <t>SE|Heat|Coal|Combined Heat and Power</t>
+  </si>
+  <si>
+    <t>{'terms': [{'variable': 'SE|Heat|+|Coal'}, {'variable': 'SE|Heat|Coal|Combined Heat and Power', 'coefficient': -1}]}</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Coal|Heat|w CCS</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Coke|Heat|w/o CCS</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Coke|Heat|w CCS</t>
+  </si>
+  <si>
     <t>Secondary Energy|Heat|Gas</t>
   </si>
   <si>
+    <t>Secondary Energy|Heat|Natural Gas|Heat|w/o CCS</t>
+  </si>
+  <si>
+    <t>SE|Heat|Gas|Combined Heat and Power</t>
+  </si>
+  <si>
+    <t>{'terms': [{'variable': 'SE|Heat|+|Gas'}, {'variable': 'SE|Heat|Gas|Combined Heat and Power', 'coefficient': -1}]}</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Natural Gas|Heat|w CCS</t>
+  </si>
+  <si>
     <t>Secondary Energy|Heat|Oil</t>
   </si>
   <si>
-    <t>Secondary Energy|Heat|Biomass</t>
-  </si>
-  <si>
-    <t>Secondary Energy|Heat|Coal</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|District Heat</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Hydrogen</t>
-  </si>
-  <si>
-    <t>Final Energy|Residential and Commercial|Hydrogen|Combustion</t>
-  </si>
-  <si>
-    <t>Final Energy|Residential and Commercial|Hydrogen|Fuel Cell</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Gas</t>
-  </si>
-  <si>
-    <t>Final Energy|Residential and Commercial|Gases</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Coal</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Biomass</t>
-  </si>
-  <si>
-    <t>Final Energy|Residential and Commercial|Electricity|Thermal|Heat Pumps</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Electricity</t>
-  </si>
-  <si>
-    <t>Final Energy|Residential and Commercial|Electricity|Thermal|Resistance</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Buildings|Oil</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Industry|Hydrogen</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Hydrogen|Combustion</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Hydrogen|Fuel Cells</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Electricity|Thermal|Resistance</t>
+    <t>Secondary Energy|Heat|Oil|Heat|w/o CCS</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Oil|Heat|w CCS</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Electricity</t>
   </si>
   <si>
     <t>SE|Heat|Electricity|Heat Pump</t>
   </si>
   <si>
-    <t>Final Energy|Industry|Other Sector|Electricity|Thermal|Heat Pumps</t>
-  </si>
-  <si>
-    <t>SE|Heat|Gas|Combined Heat and Power</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Industry|Gas</t>
-  </si>
-  <si>
-    <t>SE|Heat|Coal|Combined Heat and Power</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Industry|Coal</t>
-  </si>
-  <si>
-    <t>SE|Heat|Biomass|+|Combined Heat and Power</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Industry|Biomass</t>
-  </si>
-  <si>
-    <t>Final Energy|Heat|Industry|Oil</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Liquids|Oil|Thermal</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Liquids|Biomass|Thermal</t>
-  </si>
-  <si>
-    <t>SE|Heat|+|Geothermal</t>
+    <t>Secondary Energy|Heat|Geothermal</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Geothermal|Heat</t>
+  </si>
+  <si>
+    <t>Secondary Energy|Heat|Nuclear</t>
   </si>
   <si>
     <t>SE|Heat|+|Solar</t>
   </si>
   <si>
-    <t>Final Energy|Heat|Industry|Solar</t>
-  </si>
-  <si>
-    <t>Final Energy|Industry|Other Sector|Solar</t>
+    <t>{'terms': [{'variable': 'Secondary Energy|Heat'}, {'variable': 'Secondary Energy|Heat|Biomass', 'coefficient': -1}, {'variable': 'Secondary Energy|Heat|Coal', 'coefficient': -1}, {'variable': 'Secondary Energy|Heat|Gas', 'coefficient': -1}, {'variable': 'Secondary Energy|Heat|Oil', 'coefficient': -1}]}</t>
   </si>
   <si>
     <t>natural gas</t>
@@ -15777,10 +15906,10 @@
         <v>2396</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>1600</v>
       </c>
       <c r="C16" t="s">
-        <v>2425</v>
+        <v>2431</v>
       </c>
       <c r="D16" t="s">
         <v>332</v>
@@ -15788,41 +15917,41 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>1600</v>
       </c>
       <c r="C17" t="s">
-        <v>2425</v>
+        <v>2432</v>
       </c>
       <c r="D17" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>1600</v>
       </c>
       <c r="C18" t="s">
-        <v>2429</v>
+        <v>2433</v>
       </c>
       <c r="D18" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="B19" t="s">
-        <v>1600</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>2431</v>
+        <v>2425</v>
       </c>
       <c r="D19" t="s">
         <v>332</v>
@@ -15830,27 +15959,27 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>856</v>
+        <v>2425</v>
       </c>
       <c r="D20" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="D21" t="s">
         <v>333</v>
@@ -15858,13 +15987,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C22" t="s">
-        <v>2432</v>
+        <v>864</v>
       </c>
       <c r="D22" t="s">
         <v>333</v>
@@ -15872,38 +16001,38 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="B23" t="s">
-        <v>1600</v>
+        <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>2433</v>
+        <v>2431</v>
       </c>
       <c r="D23" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2397</v>
+        <v>2401</v>
       </c>
       <c r="B24" t="s">
-        <v>1600</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>2434</v>
+        <v>2425</v>
       </c>
       <c r="D24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="B25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>2425</v>
@@ -15914,13 +16043,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="B26" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>2425</v>
+        <v>2429</v>
       </c>
       <c r="D26" t="s">
         <v>332</v>
@@ -15928,41 +16057,41 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>1600</v>
       </c>
       <c r="C27" t="s">
-        <v>864</v>
+        <v>2434</v>
       </c>
       <c r="D27" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B28" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>864</v>
+        <v>2435</v>
       </c>
       <c r="D28" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>2431</v>
+        <v>2436</v>
       </c>
       <c r="D29" t="s">
         <v>332</v>
@@ -15970,44 +16099,44 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B30" t="s">
-        <v>1600</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>2435</v>
+        <v>856</v>
       </c>
       <c r="D30" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
-        <v>2436</v>
+        <v>856</v>
       </c>
       <c r="D31" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
         <v>2437</v>
       </c>
       <c r="D32" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -16060,7 +16189,7 @@
         <v>1600</v>
       </c>
       <c r="C36" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="D36" t="s">
         <v>332</v>
@@ -16088,7 +16217,7 @@
         <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="D38" t="s">
         <v>332</v>
@@ -17829,7 +17958,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D115"/>
+  <dimension ref="A1:D168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -17851,10 +17980,10 @@
         <v>2528</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2559</v>
+        <v>759</v>
       </c>
       <c r="D2" t="s">
         <v>332</v>
@@ -17862,13 +17991,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2560</v>
+        <v>759</v>
       </c>
       <c r="D3" t="s">
         <v>332</v>
@@ -17876,13 +18005,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>2561</v>
+        <v>2577</v>
       </c>
       <c r="D4" t="s">
         <v>332</v>
@@ -17890,13 +18019,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2531</v>
+        <v>2528</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>2562</v>
+        <v>761</v>
       </c>
       <c r="D5" t="s">
         <v>332</v>
@@ -17904,13 +18033,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>759</v>
+        <v>825</v>
       </c>
       <c r="D6" t="s">
         <v>332</v>
@@ -17918,13 +18047,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D7" t="s">
         <v>332</v>
@@ -17932,13 +18061,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>2563</v>
+        <v>824</v>
       </c>
       <c r="D8" t="s">
         <v>332</v>
@@ -17946,13 +18075,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2532</v>
+        <v>2528</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D9" t="s">
         <v>332</v>
@@ -17960,13 +18089,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>825</v>
+        <v>778</v>
       </c>
       <c r="D10" t="s">
         <v>332</v>
@@ -17974,13 +18103,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>760</v>
+        <v>778</v>
       </c>
       <c r="D11" t="s">
         <v>332</v>
@@ -17988,13 +18117,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>824</v>
+        <v>2578</v>
       </c>
       <c r="D12" t="s">
         <v>332</v>
@@ -18002,13 +18131,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2532</v>
+        <v>2529</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>762</v>
+        <v>780</v>
       </c>
       <c r="D13" t="s">
         <v>332</v>
@@ -18016,13 +18145,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>778</v>
+        <v>827</v>
       </c>
       <c r="D14" t="s">
         <v>332</v>
@@ -18030,13 +18159,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D15" t="s">
         <v>332</v>
@@ -18044,13 +18173,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>2564</v>
+        <v>826</v>
       </c>
       <c r="D16" t="s">
         <v>332</v>
@@ -18058,13 +18187,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2533</v>
+        <v>2529</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>780</v>
+        <v>2579</v>
       </c>
       <c r="D17" t="s">
         <v>332</v>
@@ -18072,13 +18201,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2533</v>
+        <v>2530</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>827</v>
+        <v>2580</v>
       </c>
       <c r="D18" t="s">
         <v>332</v>
@@ -18086,13 +18215,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="D19" t="s">
         <v>332</v>
@@ -18100,13 +18229,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C20" t="s">
-        <v>826</v>
+        <v>771</v>
       </c>
       <c r="D20" t="s">
         <v>332</v>
@@ -18114,13 +18243,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
-        <v>2565</v>
+        <v>2581</v>
       </c>
       <c r="D21" t="s">
         <v>332</v>
@@ -18128,13 +18257,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2534</v>
+        <v>2531</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
-        <v>2566</v>
+        <v>773</v>
       </c>
       <c r="D22" t="s">
         <v>332</v>
@@ -18142,13 +18271,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
-        <v>771</v>
+        <v>836</v>
       </c>
       <c r="D23" t="s">
         <v>332</v>
@@ -18156,13 +18285,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D24" t="s">
         <v>332</v>
@@ -18170,13 +18299,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>2567</v>
+        <v>837</v>
       </c>
       <c r="D25" t="s">
         <v>332</v>
@@ -18184,13 +18313,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2535</v>
+        <v>2531</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D26" t="s">
         <v>332</v>
@@ -18198,13 +18327,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2535</v>
+        <v>2532</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>836</v>
+        <v>785</v>
       </c>
       <c r="D27" t="s">
         <v>332</v>
@@ -18212,13 +18341,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="D28" t="s">
         <v>332</v>
@@ -18226,13 +18355,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>837</v>
+        <v>789</v>
       </c>
       <c r="D29" t="s">
         <v>332</v>
@@ -18240,13 +18369,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>2568</v>
+        <v>790</v>
       </c>
       <c r="D30" t="s">
         <v>332</v>
@@ -18254,13 +18383,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D31" t="s">
         <v>332</v>
@@ -18268,13 +18397,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="B32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
         <v>332</v>
@@ -18282,13 +18411,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2537</v>
+        <v>2534</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D33" t="s">
         <v>332</v>
@@ -18296,13 +18425,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D34" t="s">
         <v>332</v>
@@ -18310,13 +18439,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2538</v>
+        <v>2535</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D35" t="s">
         <v>332</v>
@@ -18324,13 +18453,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2539</v>
+        <v>2535</v>
       </c>
       <c r="B36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D36" t="s">
         <v>332</v>
@@ -18338,13 +18467,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2539</v>
+        <v>2536</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="D37" t="s">
         <v>332</v>
@@ -18352,10 +18481,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
         <v>798</v>
@@ -18366,13 +18495,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>798</v>
+        <v>2582</v>
       </c>
       <c r="D39" t="s">
         <v>332</v>
@@ -18380,13 +18509,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>2569</v>
+        <v>800</v>
       </c>
       <c r="D40" t="s">
         <v>332</v>
@@ -18394,13 +18523,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B41" t="s">
         <v>22</v>
       </c>
       <c r="C41" t="s">
-        <v>800</v>
+        <v>831</v>
       </c>
       <c r="D41" t="s">
         <v>332</v>
@@ -18408,13 +18537,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B42" t="s">
         <v>22</v>
       </c>
       <c r="C42" t="s">
-        <v>831</v>
+        <v>799</v>
       </c>
       <c r="D42" t="s">
         <v>332</v>
@@ -18422,13 +18551,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>799</v>
+        <v>830</v>
       </c>
       <c r="D43" t="s">
         <v>332</v>
@@ -18436,13 +18565,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2540</v>
+        <v>2536</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C44" t="s">
-        <v>830</v>
+        <v>803</v>
       </c>
       <c r="D44" t="s">
         <v>332</v>
@@ -18450,13 +18579,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2540</v>
+        <v>2537</v>
       </c>
       <c r="B45" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="D45" t="s">
         <v>332</v>
@@ -18464,10 +18593,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C46" t="s">
         <v>810</v>
@@ -18478,13 +18607,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C47" t="s">
-        <v>810</v>
+        <v>2583</v>
       </c>
       <c r="D47" t="s">
         <v>332</v>
@@ -18492,13 +18621,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>2570</v>
+        <v>812</v>
       </c>
       <c r="D48" t="s">
         <v>332</v>
@@ -18506,13 +18635,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B49" t="s">
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>812</v>
+        <v>835</v>
       </c>
       <c r="D49" t="s">
         <v>332</v>
@@ -18520,13 +18649,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B50" t="s">
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>835</v>
+        <v>811</v>
       </c>
       <c r="D50" t="s">
         <v>332</v>
@@ -18534,13 +18663,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B51" t="s">
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>811</v>
+        <v>834</v>
       </c>
       <c r="D51" t="s">
         <v>332</v>
@@ -18548,13 +18677,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2541</v>
+        <v>2537</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C52" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="D52" t="s">
         <v>332</v>
@@ -18562,13 +18691,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2541</v>
+        <v>2538</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="D53" t="s">
         <v>332</v>
@@ -18576,10 +18705,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C54" t="s">
         <v>804</v>
@@ -18590,13 +18719,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="D55" t="s">
         <v>332</v>
@@ -18604,13 +18733,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B56" t="s">
         <v>22</v>
       </c>
       <c r="C56" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="D56" t="s">
         <v>332</v>
@@ -18618,13 +18747,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B57" t="s">
         <v>22</v>
       </c>
       <c r="C57" t="s">
-        <v>833</v>
+        <v>805</v>
       </c>
       <c r="D57" t="s">
         <v>332</v>
@@ -18632,13 +18761,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B58" t="s">
         <v>22</v>
       </c>
       <c r="C58" t="s">
-        <v>805</v>
+        <v>832</v>
       </c>
       <c r="D58" t="s">
         <v>332</v>
@@ -18646,13 +18775,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2542</v>
+        <v>2538</v>
       </c>
       <c r="B59" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
-        <v>832</v>
+        <v>809</v>
       </c>
       <c r="D59" t="s">
         <v>332</v>
@@ -18660,13 +18789,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2542</v>
+        <v>2539</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>809</v>
+        <v>765</v>
       </c>
       <c r="D60" t="s">
         <v>332</v>
@@ -18674,10 +18803,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C61" t="s">
         <v>765</v>
@@ -18688,13 +18817,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2543</v>
+        <v>2539</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C62" t="s">
-        <v>765</v>
+        <v>2584</v>
       </c>
       <c r="D62" t="s">
         <v>332</v>
@@ -18702,13 +18831,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2543</v>
+        <v>2540</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>2571</v>
+        <v>768</v>
       </c>
       <c r="D63" t="s">
         <v>332</v>
@@ -18716,10 +18845,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
         <v>768</v>
@@ -18730,13 +18859,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B65" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C65" t="s">
-        <v>768</v>
+        <v>2585</v>
       </c>
       <c r="D65" t="s">
         <v>332</v>
@@ -18744,13 +18873,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>2572</v>
+        <v>767</v>
       </c>
       <c r="D66" t="s">
         <v>332</v>
@@ -18758,13 +18887,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>767</v>
+        <v>823</v>
       </c>
       <c r="D67" t="s">
         <v>332</v>
@@ -18772,13 +18901,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B68" t="s">
         <v>22</v>
       </c>
       <c r="C68" t="s">
-        <v>823</v>
+        <v>766</v>
       </c>
       <c r="D68" t="s">
         <v>332</v>
@@ -18786,13 +18915,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
       </c>
       <c r="C69" t="s">
-        <v>766</v>
+        <v>822</v>
       </c>
       <c r="D69" t="s">
         <v>332</v>
@@ -18800,13 +18929,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2544</v>
+        <v>2540</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C70" t="s">
-        <v>822</v>
+        <v>2586</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -18814,13 +18943,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2544</v>
+        <v>2541</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>2573</v>
+        <v>791</v>
       </c>
       <c r="D71" t="s">
         <v>332</v>
@@ -18828,10 +18957,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B72" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
         <v>791</v>
@@ -18842,13 +18971,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B73" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D73" t="s">
         <v>332</v>
@@ -18856,13 +18985,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B74" t="s">
         <v>22</v>
       </c>
       <c r="C74" t="s">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="D74" t="s">
         <v>332</v>
@@ -18870,13 +18999,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
       </c>
       <c r="C75" t="s">
-        <v>829</v>
+        <v>792</v>
       </c>
       <c r="D75" t="s">
         <v>332</v>
@@ -18884,13 +19013,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>792</v>
+        <v>828</v>
       </c>
       <c r="D76" t="s">
         <v>332</v>
@@ -18898,13 +19027,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C77" t="s">
-        <v>828</v>
+        <v>2587</v>
       </c>
       <c r="D77" t="s">
         <v>332</v>
@@ -18912,13 +19041,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2545</v>
+        <v>2541</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
-        <v>2574</v>
+        <v>796</v>
       </c>
       <c r="D78" t="s">
         <v>332</v>
@@ -18926,13 +19055,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2545</v>
+        <v>2542</v>
       </c>
       <c r="B79" t="s">
         <v>25</v>
       </c>
       <c r="C79" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="D79" t="s">
         <v>332</v>
@@ -18940,13 +19069,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B80" t="s">
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>1070</v>
+        <v>1089</v>
       </c>
       <c r="D80" t="s">
         <v>332</v>
@@ -18954,13 +19083,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>2575</v>
+        <v>2588</v>
       </c>
       <c r="D81" t="s">
         <v>332</v>
@@ -18968,13 +19097,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2546</v>
+        <v>2543</v>
       </c>
       <c r="B82" t="s">
         <v>25</v>
       </c>
       <c r="C82" t="s">
-        <v>2576</v>
+        <v>1089</v>
       </c>
       <c r="D82" t="s">
         <v>332</v>
@@ -18982,13 +19111,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2547</v>
+        <v>2543</v>
       </c>
       <c r="B83" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C83" t="s">
-        <v>2577</v>
+        <v>2589</v>
       </c>
       <c r="D83" t="s">
         <v>332</v>
@@ -18996,13 +19125,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2548</v>
+        <v>2543</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C84" t="s">
-        <v>2578</v>
+        <v>2589</v>
       </c>
       <c r="D84" t="s">
         <v>332</v>
@@ -19010,13 +19139,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C85" t="s">
-        <v>2579</v>
+        <v>1070</v>
       </c>
       <c r="D85" t="s">
         <v>332</v>
@@ -19024,13 +19153,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="B86" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>2579</v>
+        <v>2590</v>
       </c>
       <c r="D86" t="s">
         <v>332</v>
@@ -19038,13 +19167,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>1064</v>
+        <v>2591</v>
       </c>
       <c r="D87" t="s">
         <v>332</v>
@@ -19052,13 +19181,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2549</v>
+        <v>2544</v>
       </c>
       <c r="B88" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>2580</v>
+        <v>2592</v>
       </c>
       <c r="D88" t="s">
         <v>332</v>
@@ -19066,13 +19195,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2550</v>
+        <v>2544</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>2581</v>
+        <v>2592</v>
       </c>
       <c r="D89" t="s">
         <v>332</v>
@@ -19080,13 +19209,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2550</v>
+        <v>2545</v>
       </c>
       <c r="B90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C90" t="s">
-        <v>2581</v>
+        <v>2593</v>
       </c>
       <c r="D90" t="s">
         <v>332</v>
@@ -19094,13 +19223,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C91" t="s">
-        <v>1079</v>
+        <v>2594</v>
       </c>
       <c r="D91" t="s">
         <v>332</v>
@@ -19108,13 +19237,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="B92" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>2582</v>
+        <v>948</v>
       </c>
       <c r="D92" t="s">
         <v>332</v>
@@ -19122,13 +19251,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2550</v>
+        <v>2546</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C93" t="s">
-        <v>1077</v>
+        <v>949</v>
       </c>
       <c r="D93" t="s">
         <v>332</v>
@@ -19136,13 +19265,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2551</v>
+        <v>2546</v>
       </c>
       <c r="B94" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C94" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="D94" t="s">
         <v>332</v>
@@ -19150,13 +19279,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="B95" t="s">
         <v>23</v>
       </c>
       <c r="C95" t="s">
-        <v>2583</v>
+        <v>1074</v>
       </c>
       <c r="D95" t="s">
         <v>332</v>
@@ -19164,13 +19293,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="B96" t="s">
         <v>24</v>
       </c>
       <c r="C96" t="s">
-        <v>2583</v>
+        <v>948</v>
       </c>
       <c r="D96" t="s">
         <v>332</v>
@@ -19178,13 +19307,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C97" t="s">
-        <v>1094</v>
+        <v>949</v>
       </c>
       <c r="D97" t="s">
         <v>332</v>
@@ -19192,13 +19321,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="B98" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C98" t="s">
-        <v>2584</v>
+        <v>1073</v>
       </c>
       <c r="D98" t="s">
         <v>332</v>
@@ -19206,13 +19335,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>2552</v>
+        <v>2546</v>
       </c>
       <c r="B99" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C99" t="s">
-        <v>1092</v>
+        <v>1074</v>
       </c>
       <c r="D99" t="s">
         <v>332</v>
@@ -19220,13 +19349,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
       <c r="B100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C100" t="s">
-        <v>2585</v>
+        <v>1064</v>
       </c>
       <c r="D100" t="s">
         <v>332</v>
@@ -19234,13 +19363,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>2553</v>
+        <v>2547</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C101" t="s">
-        <v>2585</v>
+        <v>2595</v>
       </c>
       <c r="D101" t="s">
         <v>332</v>
@@ -19248,13 +19377,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
       </c>
       <c r="C102" t="s">
-        <v>1089</v>
+        <v>1079</v>
       </c>
       <c r="D102" t="s">
         <v>332</v>
@@ -19262,13 +19391,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="B103" t="s">
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>2586</v>
+        <v>2596</v>
       </c>
       <c r="D103" t="s">
         <v>332</v>
@@ -19276,13 +19405,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>2553</v>
+        <v>2548</v>
       </c>
       <c r="B104" t="s">
         <v>25</v>
       </c>
       <c r="C104" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
       <c r="D104" t="s">
         <v>332</v>
@@ -19290,13 +19419,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>2554</v>
+        <v>2548</v>
       </c>
       <c r="B105" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C105" t="s">
-        <v>1086</v>
+        <v>2597</v>
       </c>
       <c r="D105" t="s">
         <v>332</v>
@@ -19304,13 +19433,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>2554</v>
+        <v>2548</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C106" t="s">
-        <v>2587</v>
+        <v>2597</v>
       </c>
       <c r="D106" t="s">
         <v>332</v>
@@ -19318,13 +19447,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>2554</v>
+        <v>2549</v>
       </c>
       <c r="B107" t="s">
         <v>25</v>
       </c>
       <c r="C107" t="s">
-        <v>2588</v>
+        <v>1076</v>
       </c>
       <c r="D107" t="s">
         <v>332</v>
@@ -19332,13 +19461,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>2555</v>
+        <v>2549</v>
       </c>
       <c r="B108" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C108" t="s">
-        <v>2589</v>
+        <v>2598</v>
       </c>
       <c r="D108" t="s">
         <v>332</v>
@@ -19346,13 +19475,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>2556</v>
+        <v>2549</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C109" t="s">
-        <v>2590</v>
+        <v>2598</v>
       </c>
       <c r="D109" t="s">
         <v>332</v>
@@ -19360,13 +19489,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>2556</v>
+        <v>2550</v>
       </c>
       <c r="B110" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C110" t="s">
-        <v>2590</v>
+        <v>1094</v>
       </c>
       <c r="D110" t="s">
         <v>332</v>
@@ -19374,13 +19503,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>2557</v>
+        <v>2550</v>
       </c>
       <c r="B111" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C111" t="s">
-        <v>2591</v>
+        <v>2599</v>
       </c>
       <c r="D111" t="s">
         <v>332</v>
@@ -19388,13 +19517,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>2557</v>
+        <v>2550</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C112" t="s">
-        <v>2591</v>
+        <v>1092</v>
       </c>
       <c r="D112" t="s">
         <v>332</v>
@@ -19402,13 +19531,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>2557</v>
+        <v>2550</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C113" t="s">
-        <v>2592</v>
+        <v>2600</v>
       </c>
       <c r="D113" t="s">
         <v>332</v>
@@ -19416,13 +19545,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>2557</v>
+        <v>2550</v>
       </c>
       <c r="B114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C114" t="s">
-        <v>2593</v>
+        <v>2600</v>
       </c>
       <c r="D114" t="s">
         <v>332</v>
@@ -19430,15 +19559,757 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B115" t="s">
+        <v>22</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D115" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B116" t="s">
+        <v>26</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D116" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B117" t="s">
+        <v>25</v>
+      </c>
+      <c r="C117" t="s">
+        <v>2602</v>
+      </c>
+      <c r="D117" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B118" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D118" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B119" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D119" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B120" t="s">
+        <v>25</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D120" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B121" t="s">
+        <v>23</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D121" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B122" t="s">
+        <v>24</v>
+      </c>
+      <c r="C122" t="s">
+        <v>2605</v>
+      </c>
+      <c r="D122" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B123" t="s">
+        <v>26</v>
+      </c>
+      <c r="C123" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D123" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B124" t="s">
+        <v>25</v>
+      </c>
+      <c r="C124" t="s">
+        <v>2607</v>
+      </c>
+      <c r="D124" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B125" t="s">
+        <v>22</v>
+      </c>
+      <c r="C125" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D125" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B126" t="s">
+        <v>26</v>
+      </c>
+      <c r="C126" t="s">
+        <v>2608</v>
+      </c>
+      <c r="D126" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B127" t="s">
+        <v>25</v>
+      </c>
+      <c r="C127" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D127" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B128" t="s">
+        <v>23</v>
+      </c>
+      <c r="C128" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D128" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B129" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" t="s">
+        <v>2609</v>
+      </c>
+      <c r="D129" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C130" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D130" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B131" t="s">
+        <v>22</v>
+      </c>
+      <c r="C131" t="s">
+        <v>2610</v>
+      </c>
+      <c r="D131" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B132" t="s">
+        <v>27</v>
+      </c>
+      <c r="C132" t="s">
+        <v>2611</v>
+      </c>
+      <c r="D132" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B133" t="s">
+        <v>23</v>
+      </c>
+      <c r="C133" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D133" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B134" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" t="s">
+        <v>2612</v>
+      </c>
+      <c r="D134" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B135" t="s">
+        <v>23</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D135" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B136" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" t="s">
+        <v>2613</v>
+      </c>
+      <c r="D136" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
         <v>2558</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B137" t="s">
+        <v>27</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2614</v>
+      </c>
+      <c r="D137" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B138" t="s">
         <v>25</v>
       </c>
-      <c r="C115" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D115" t="s">
+      <c r="C138" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D138" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D139" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B140" t="s">
+        <v>27</v>
+      </c>
+      <c r="C140" t="s">
+        <v>2616</v>
+      </c>
+      <c r="D140" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B141" t="s">
+        <v>23</v>
+      </c>
+      <c r="C141" t="s">
+        <v>2617</v>
+      </c>
+      <c r="D141" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B142" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" t="s">
+        <v>2617</v>
+      </c>
+      <c r="D142" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B143" t="s">
+        <v>23</v>
+      </c>
+      <c r="C143" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D143" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B144" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" t="s">
+        <v>2618</v>
+      </c>
+      <c r="D144" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B145" t="s">
+        <v>27</v>
+      </c>
+      <c r="C145" t="s">
+        <v>2619</v>
+      </c>
+      <c r="D145" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B146" t="s">
+        <v>27</v>
+      </c>
+      <c r="C146" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D146" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B147" t="s">
+        <v>27</v>
+      </c>
+      <c r="C147" t="s">
+        <v>2621</v>
+      </c>
+      <c r="D147" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B148" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D148" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B149" t="s">
+        <v>22</v>
+      </c>
+      <c r="C149" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D149" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B150" t="s">
+        <v>27</v>
+      </c>
+      <c r="C150" t="s">
+        <v>2623</v>
+      </c>
+      <c r="D150" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B151" t="s">
+        <v>23</v>
+      </c>
+      <c r="C151" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D151" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B152" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" t="s">
+        <v>2624</v>
+      </c>
+      <c r="D152" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B153" t="s">
+        <v>23</v>
+      </c>
+      <c r="C153" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D153" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B154" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" t="s">
+        <v>2625</v>
+      </c>
+      <c r="D154" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C155" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D155" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B156" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D156" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B157" t="s">
+        <v>22</v>
+      </c>
+      <c r="C157" t="s">
+        <v>2627</v>
+      </c>
+      <c r="D157" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B158" t="s">
+        <v>27</v>
+      </c>
+      <c r="C158" t="s">
+        <v>2628</v>
+      </c>
+      <c r="D158" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B159" t="s">
+        <v>27</v>
+      </c>
+      <c r="C159" t="s">
+        <v>2629</v>
+      </c>
+      <c r="D159" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B160" t="s">
+        <v>25</v>
+      </c>
+      <c r="C160" t="s">
+        <v>2630</v>
+      </c>
+      <c r="D160" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B161" t="s">
+        <v>23</v>
+      </c>
+      <c r="C161" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D161" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B162" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" t="s">
+        <v>2631</v>
+      </c>
+      <c r="D162" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B163" t="s">
+        <v>25</v>
+      </c>
+      <c r="C163" t="s">
+        <v>2632</v>
+      </c>
+      <c r="D163" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B164" t="s">
+        <v>27</v>
+      </c>
+      <c r="C164" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D164" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B165" t="s">
+        <v>25</v>
+      </c>
+      <c r="C165" t="s">
+        <v>2634</v>
+      </c>
+      <c r="D165" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B166" t="s">
+        <v>23</v>
+      </c>
+      <c r="C166" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D166" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B167" t="s">
+        <v>24</v>
+      </c>
+      <c r="C167" t="s">
+        <v>2635</v>
+      </c>
+      <c r="D167" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B168" t="s">
+        <v>22</v>
+      </c>
+      <c r="C168" t="s">
+        <v>2636</v>
+      </c>
+      <c r="D168" t="s">
         <v>332</v>
       </c>
     </row>
@@ -19468,13 +20339,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>2706</v>
+        <v>2749</v>
       </c>
       <c r="D2" t="s">
         <v>332</v>
@@ -19482,13 +20353,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>2707</v>
+        <v>2750</v>
       </c>
       <c r="D3" t="s">
         <v>332</v>
@@ -19496,13 +20367,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>2707</v>
+        <v>2750</v>
       </c>
       <c r="D4" t="s">
         <v>332</v>
@@ -19510,13 +20381,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>2708</v>
+        <v>2751</v>
       </c>
       <c r="D5" t="s">
         <v>332</v>
@@ -19524,13 +20395,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>2709</v>
+        <v>2752</v>
       </c>
       <c r="D6" t="s">
         <v>332</v>
@@ -19538,13 +20409,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2594</v>
+        <v>2637</v>
       </c>
       <c r="B7" t="s">
         <v>1600</v>
       </c>
       <c r="C7" t="s">
-        <v>2710</v>
+        <v>2753</v>
       </c>
       <c r="D7" t="s">
         <v>332</v>
@@ -19552,13 +20423,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>2711</v>
+        <v>2754</v>
       </c>
       <c r="D8" t="s">
         <v>332</v>
@@ -19566,13 +20437,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>2712</v>
+        <v>2755</v>
       </c>
       <c r="D9" t="s">
         <v>332</v>
@@ -19580,13 +20451,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2713</v>
+        <v>2756</v>
       </c>
       <c r="D10" t="s">
         <v>332</v>
@@ -19594,13 +20465,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2713</v>
+        <v>2756</v>
       </c>
       <c r="D11" t="s">
         <v>332</v>
@@ -19608,13 +20479,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>2714</v>
+        <v>2757</v>
       </c>
       <c r="D12" t="s">
         <v>332</v>
@@ -19622,13 +20493,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B13" t="s">
         <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>2711</v>
+        <v>2754</v>
       </c>
       <c r="D13" t="s">
         <v>332</v>
@@ -19636,13 +20507,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2595</v>
+        <v>2638</v>
       </c>
       <c r="B14" t="s">
         <v>1600</v>
       </c>
       <c r="C14" t="s">
-        <v>2715</v>
+        <v>2758</v>
       </c>
       <c r="D14" t="s">
         <v>332</v>
@@ -19650,13 +20521,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2596</v>
+        <v>2639</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>2716</v>
+        <v>2759</v>
       </c>
       <c r="D15" t="s">
         <v>332</v>
@@ -19664,13 +20535,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2596</v>
+        <v>2639</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2717</v>
+        <v>2760</v>
       </c>
       <c r="D16" t="s">
         <v>332</v>
@@ -19678,13 +20549,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2596</v>
+        <v>2639</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2717</v>
+        <v>2760</v>
       </c>
       <c r="D17" t="s">
         <v>332</v>
@@ -19692,13 +20563,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2596</v>
+        <v>2639</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
       <c r="C18" t="s">
-        <v>2718</v>
+        <v>2761</v>
       </c>
       <c r="D18" t="s">
         <v>332</v>
@@ -19706,13 +20577,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2596</v>
+        <v>2639</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>2719</v>
+        <v>2762</v>
       </c>
       <c r="D19" t="s">
         <v>332</v>
@@ -19720,13 +20591,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2597</v>
+        <v>2640</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>2720</v>
+        <v>2763</v>
       </c>
       <c r="D20" t="s">
         <v>2105</v>
@@ -19734,13 +20605,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2597</v>
+        <v>2640</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
       </c>
       <c r="C21" t="s">
-        <v>2720</v>
+        <v>2763</v>
       </c>
       <c r="D21" t="s">
         <v>2105</v>
@@ -19748,13 +20619,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2597</v>
+        <v>2640</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2721</v>
+        <v>2764</v>
       </c>
       <c r="D22" t="s">
         <v>2105</v>
@@ -19762,13 +20633,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2598</v>
+        <v>2641</v>
       </c>
       <c r="B23" t="s">
         <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>2722</v>
+        <v>2765</v>
       </c>
       <c r="D23" t="s">
         <v>332</v>
@@ -19776,13 +20647,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2598</v>
+        <v>2641</v>
       </c>
       <c r="B24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>2722</v>
+        <v>2765</v>
       </c>
       <c r="D24" t="s">
         <v>332</v>
@@ -19790,13 +20661,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2599</v>
+        <v>2642</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
-        <v>2723</v>
+        <v>2766</v>
       </c>
       <c r="D25" t="s">
         <v>332</v>
@@ -19804,13 +20675,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B26" t="s">
         <v>26</v>
       </c>
       <c r="C26" t="s">
-        <v>2724</v>
+        <v>2767</v>
       </c>
       <c r="D26" t="s">
         <v>332</v>
@@ -19818,13 +20689,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B27" t="s">
         <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>2725</v>
+        <v>2768</v>
       </c>
       <c r="D27" t="s">
         <v>332</v>
@@ -19832,13 +20703,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>2725</v>
+        <v>2768</v>
       </c>
       <c r="D28" t="s">
         <v>332</v>
@@ -19846,13 +20717,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>2726</v>
+        <v>2769</v>
       </c>
       <c r="D29" t="s">
         <v>332</v>
@@ -19860,13 +20731,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>2727</v>
+        <v>2770</v>
       </c>
       <c r="D30" t="s">
         <v>332</v>
@@ -19874,13 +20745,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2600</v>
+        <v>2643</v>
       </c>
       <c r="B31" t="s">
         <v>1600</v>
       </c>
       <c r="C31" t="s">
-        <v>2728</v>
+        <v>2771</v>
       </c>
       <c r="D31" t="s">
         <v>332</v>
@@ -19888,13 +20759,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>2729</v>
+        <v>2772</v>
       </c>
       <c r="D32" t="s">
         <v>332</v>
@@ -19902,13 +20773,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B33" t="s">
         <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>2730</v>
+        <v>2773</v>
       </c>
       <c r="D33" t="s">
         <v>332</v>
@@ -19916,13 +20787,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B34" t="s">
         <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>2731</v>
+        <v>2774</v>
       </c>
       <c r="D34" t="s">
         <v>332</v>
@@ -19930,13 +20801,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
       </c>
       <c r="C35" t="s">
-        <v>2731</v>
+        <v>2774</v>
       </c>
       <c r="D35" t="s">
         <v>332</v>
@@ -19944,13 +20815,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B36" t="s">
         <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>2732</v>
+        <v>2775</v>
       </c>
       <c r="D36" t="s">
         <v>332</v>
@@ -19958,13 +20829,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B37" t="s">
         <v>25</v>
       </c>
       <c r="C37" t="s">
-        <v>2733</v>
+        <v>2776</v>
       </c>
       <c r="D37" t="s">
         <v>332</v>
@@ -19972,13 +20843,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>2601</v>
+        <v>2644</v>
       </c>
       <c r="B38" t="s">
         <v>1600</v>
       </c>
       <c r="C38" t="s">
-        <v>2734</v>
+        <v>2777</v>
       </c>
       <c r="D38" t="s">
         <v>332</v>
@@ -19986,13 +20857,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>2602</v>
+        <v>2645</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
       </c>
       <c r="C39" t="s">
-        <v>2735</v>
+        <v>2778</v>
       </c>
       <c r="D39" t="s">
         <v>2105</v>
@@ -20000,13 +20871,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>2602</v>
+        <v>2645</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
       </c>
       <c r="C40" t="s">
-        <v>2735</v>
+        <v>2778</v>
       </c>
       <c r="D40" t="s">
         <v>2105</v>
@@ -20014,13 +20885,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>2736</v>
+        <v>2779</v>
       </c>
       <c r="D41" t="s">
         <v>332</v>
@@ -20028,13 +20899,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B42" t="s">
         <v>26</v>
       </c>
       <c r="C42" t="s">
-        <v>2737</v>
+        <v>2780</v>
       </c>
       <c r="D42" t="s">
         <v>332</v>
@@ -20042,13 +20913,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
       <c r="C43" t="s">
-        <v>2738</v>
+        <v>2781</v>
       </c>
       <c r="D43" t="s">
         <v>332</v>
@@ -20056,13 +20927,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B44" t="s">
         <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>2738</v>
+        <v>2781</v>
       </c>
       <c r="D44" t="s">
         <v>332</v>
@@ -20070,13 +20941,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
       </c>
       <c r="C45" t="s">
-        <v>2739</v>
+        <v>2782</v>
       </c>
       <c r="D45" t="s">
         <v>332</v>
@@ -20084,13 +20955,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B46" t="s">
         <v>25</v>
       </c>
       <c r="C46" t="s">
-        <v>2733</v>
+        <v>2776</v>
       </c>
       <c r="D46" t="s">
         <v>332</v>
@@ -20098,13 +20969,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>2603</v>
+        <v>2646</v>
       </c>
       <c r="B47" t="s">
         <v>1600</v>
       </c>
       <c r="C47" t="s">
-        <v>2740</v>
+        <v>2783</v>
       </c>
       <c r="D47" t="s">
         <v>332</v>
@@ -20112,13 +20983,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>2604</v>
+        <v>2647</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>2735</v>
+        <v>2778</v>
       </c>
       <c r="D48" t="s">
         <v>2105</v>
@@ -20126,13 +20997,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>2604</v>
+        <v>2647</v>
       </c>
       <c r="B49" t="s">
         <v>24</v>
       </c>
       <c r="C49" t="s">
-        <v>2735</v>
+        <v>2778</v>
       </c>
       <c r="D49" t="s">
         <v>2105</v>
@@ -20140,13 +21011,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>2605</v>
+        <v>2648</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>2741</v>
+        <v>2784</v>
       </c>
       <c r="D50" t="s">
         <v>332</v>
@@ -20154,13 +21025,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>2605</v>
+        <v>2648</v>
       </c>
       <c r="B51" t="s">
         <v>24</v>
       </c>
       <c r="C51" t="s">
-        <v>2741</v>
+        <v>2784</v>
       </c>
       <c r="D51" t="s">
         <v>332</v>
@@ -20168,13 +21039,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>2605</v>
+        <v>2648</v>
       </c>
       <c r="B52" t="s">
         <v>1600</v>
       </c>
       <c r="C52" t="s">
-        <v>2742</v>
+        <v>2785</v>
       </c>
       <c r="D52" t="s">
         <v>332</v>
@@ -20182,13 +21053,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>2606</v>
+        <v>2649</v>
       </c>
       <c r="B53" t="s">
         <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>2743</v>
+        <v>2786</v>
       </c>
       <c r="D53" t="s">
         <v>2105</v>
@@ -20196,13 +21067,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>2606</v>
+        <v>2649</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>2743</v>
+        <v>2786</v>
       </c>
       <c r="D54" t="s">
         <v>2105</v>
@@ -20210,13 +21081,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>2607</v>
+        <v>2650</v>
       </c>
       <c r="B55" t="s">
         <v>23</v>
       </c>
       <c r="C55" t="s">
-        <v>2744</v>
+        <v>2787</v>
       </c>
       <c r="D55" t="s">
         <v>332</v>
@@ -20224,13 +21095,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>2607</v>
+        <v>2650</v>
       </c>
       <c r="B56" t="s">
         <v>24</v>
       </c>
       <c r="C56" t="s">
-        <v>2744</v>
+        <v>2787</v>
       </c>
       <c r="D56" t="s">
         <v>332</v>
@@ -20238,13 +21109,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>2607</v>
+        <v>2650</v>
       </c>
       <c r="B57" t="s">
         <v>25</v>
       </c>
       <c r="C57" t="s">
-        <v>2745</v>
+        <v>2788</v>
       </c>
       <c r="D57" t="s">
         <v>332</v>
@@ -20252,13 +21123,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>2607</v>
+        <v>2650</v>
       </c>
       <c r="B58" t="s">
         <v>1600</v>
       </c>
       <c r="C58" t="s">
-        <v>2746</v>
+        <v>2789</v>
       </c>
       <c r="D58" t="s">
         <v>332</v>
@@ -20266,13 +21137,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>2608</v>
+        <v>2651</v>
       </c>
       <c r="B59" t="s">
         <v>23</v>
       </c>
       <c r="C59" t="s">
-        <v>2747</v>
+        <v>2790</v>
       </c>
       <c r="D59" t="s">
         <v>2105</v>
@@ -20280,13 +21151,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>2608</v>
+        <v>2651</v>
       </c>
       <c r="B60" t="s">
         <v>24</v>
       </c>
       <c r="C60" t="s">
-        <v>2747</v>
+        <v>2790</v>
       </c>
       <c r="D60" t="s">
         <v>2105</v>
@@ -20294,13 +21165,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>2609</v>
+        <v>2652</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>2748</v>
+        <v>2791</v>
       </c>
       <c r="D61" t="s">
         <v>332</v>
@@ -20308,13 +21179,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>2609</v>
+        <v>2652</v>
       </c>
       <c r="B62" t="s">
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>2748</v>
+        <v>2791</v>
       </c>
       <c r="D62" t="s">
         <v>332</v>
@@ -20322,13 +21193,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>2609</v>
+        <v>2652</v>
       </c>
       <c r="B63" t="s">
         <v>25</v>
       </c>
       <c r="C63" t="s">
-        <v>2749</v>
+        <v>2792</v>
       </c>
       <c r="D63" t="s">
         <v>332</v>
@@ -20336,13 +21207,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>2609</v>
+        <v>2652</v>
       </c>
       <c r="B64" t="s">
         <v>1600</v>
       </c>
       <c r="C64" t="s">
-        <v>2750</v>
+        <v>2793</v>
       </c>
       <c r="D64" t="s">
         <v>332</v>
@@ -20350,13 +21221,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>2610</v>
+        <v>2653</v>
       </c>
       <c r="B65" t="s">
         <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>2751</v>
+        <v>2794</v>
       </c>
       <c r="D65" t="s">
         <v>2105</v>
@@ -20364,13 +21235,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>2610</v>
+        <v>2653</v>
       </c>
       <c r="B66" t="s">
         <v>24</v>
       </c>
       <c r="C66" t="s">
-        <v>2751</v>
+        <v>2794</v>
       </c>
       <c r="D66" t="s">
         <v>2105</v>
@@ -20378,13 +21249,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>2611</v>
+        <v>2654</v>
       </c>
       <c r="B67" t="s">
         <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>2752</v>
+        <v>2795</v>
       </c>
       <c r="D67" t="s">
         <v>332</v>
@@ -20392,13 +21263,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>2611</v>
+        <v>2654</v>
       </c>
       <c r="B68" t="s">
         <v>23</v>
       </c>
       <c r="C68" t="s">
-        <v>2741</v>
+        <v>2784</v>
       </c>
       <c r="D68" t="s">
         <v>332</v>
@@ -20406,13 +21277,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>2611</v>
+        <v>2654</v>
       </c>
       <c r="B69" t="s">
         <v>24</v>
       </c>
       <c r="C69" t="s">
-        <v>2741</v>
+        <v>2784</v>
       </c>
       <c r="D69" t="s">
         <v>332</v>
@@ -20420,13 +21291,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>2611</v>
+        <v>2654</v>
       </c>
       <c r="B70" t="s">
         <v>1600</v>
       </c>
       <c r="C70" t="s">
-        <v>2742</v>
+        <v>2785</v>
       </c>
       <c r="D70" t="s">
         <v>332</v>
@@ -20434,13 +21305,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B71" t="s">
         <v>27</v>
       </c>
       <c r="C71" t="s">
-        <v>2753</v>
+        <v>2796</v>
       </c>
       <c r="D71" t="s">
         <v>332</v>
@@ -20448,13 +21319,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>2744</v>
+        <v>2787</v>
       </c>
       <c r="D72" t="s">
         <v>332</v>
@@ -20462,13 +21333,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B73" t="s">
         <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>2744</v>
+        <v>2787</v>
       </c>
       <c r="D73" t="s">
         <v>332</v>
@@ -20476,13 +21347,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B74" t="s">
         <v>25</v>
       </c>
       <c r="C74" t="s">
-        <v>2754</v>
+        <v>2797</v>
       </c>
       <c r="D74" t="s">
         <v>332</v>
@@ -20490,13 +21361,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B75" t="s">
         <v>1600</v>
       </c>
       <c r="C75" t="s">
-        <v>2746</v>
+        <v>2789</v>
       </c>
       <c r="D75" t="s">
         <v>332</v>
@@ -20504,13 +21375,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>2612</v>
+        <v>2655</v>
       </c>
       <c r="B76" t="s">
         <v>26</v>
       </c>
       <c r="C76" t="s">
-        <v>2755</v>
+        <v>2798</v>
       </c>
       <c r="D76" t="s">
         <v>332</v>
@@ -20518,13 +21389,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>2613</v>
+        <v>2656</v>
       </c>
       <c r="B77" t="s">
         <v>27</v>
       </c>
       <c r="C77" t="s">
-        <v>2756</v>
+        <v>2799</v>
       </c>
       <c r="D77" t="s">
         <v>2105</v>
@@ -20532,13 +21403,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>2613</v>
+        <v>2656</v>
       </c>
       <c r="B78" t="s">
         <v>23</v>
       </c>
       <c r="C78" t="s">
-        <v>2747</v>
+        <v>2790</v>
       </c>
       <c r="D78" t="s">
         <v>2105</v>
@@ -20546,13 +21417,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>2613</v>
+        <v>2656</v>
       </c>
       <c r="B79" t="s">
         <v>24</v>
       </c>
       <c r="C79" t="s">
-        <v>2747</v>
+        <v>2790</v>
       </c>
       <c r="D79" t="s">
         <v>2105</v>
@@ -20560,13 +21431,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>2613</v>
+        <v>2656</v>
       </c>
       <c r="B80" t="s">
         <v>26</v>
       </c>
       <c r="C80" t="s">
-        <v>2757</v>
+        <v>2800</v>
       </c>
       <c r="D80" t="s">
         <v>2105</v>
@@ -20574,13 +21445,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B81" t="s">
         <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>2758</v>
+        <v>2801</v>
       </c>
       <c r="D81" t="s">
         <v>332</v>
@@ -20588,13 +21459,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B82" t="s">
         <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>2748</v>
+        <v>2791</v>
       </c>
       <c r="D82" t="s">
         <v>332</v>
@@ -20602,13 +21473,13 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B83" t="s">
         <v>24</v>
       </c>
       <c r="C83" t="s">
-        <v>2748</v>
+        <v>2791</v>
       </c>
       <c r="D83" t="s">
         <v>332</v>
@@ -20616,13 +21487,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B84" t="s">
         <v>25</v>
       </c>
       <c r="C84" t="s">
-        <v>2759</v>
+        <v>2802</v>
       </c>
       <c r="D84" t="s">
         <v>332</v>
@@ -20630,13 +21501,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B85" t="s">
         <v>1600</v>
       </c>
       <c r="C85" t="s">
-        <v>2750</v>
+        <v>2793</v>
       </c>
       <c r="D85" t="s">
         <v>332</v>
@@ -20644,13 +21515,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>2614</v>
+        <v>2657</v>
       </c>
       <c r="B86" t="s">
         <v>26</v>
       </c>
       <c r="C86" t="s">
-        <v>2760</v>
+        <v>2803</v>
       </c>
       <c r="D86" t="s">
         <v>332</v>
@@ -20658,13 +21529,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>2615</v>
+        <v>2658</v>
       </c>
       <c r="B87" t="s">
         <v>27</v>
       </c>
       <c r="C87" t="s">
-        <v>2761</v>
+        <v>2804</v>
       </c>
       <c r="D87" t="s">
         <v>2105</v>
@@ -20672,13 +21543,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>2615</v>
+        <v>2658</v>
       </c>
       <c r="B88" t="s">
         <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>2751</v>
+        <v>2794</v>
       </c>
       <c r="D88" t="s">
         <v>2105</v>
@@ -20686,13 +21557,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>2615</v>
+        <v>2658</v>
       </c>
       <c r="B89" t="s">
         <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>2751</v>
+        <v>2794</v>
       </c>
       <c r="D89" t="s">
         <v>2105</v>
@@ -20700,13 +21571,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>2615</v>
+        <v>2658</v>
       </c>
       <c r="B90" t="s">
         <v>26</v>
       </c>
       <c r="C90" t="s">
-        <v>2762</v>
+        <v>2805</v>
       </c>
       <c r="D90" t="s">
         <v>2105</v>
@@ -20714,13 +21585,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B91" t="s">
         <v>27</v>
       </c>
       <c r="C91" t="s">
-        <v>2763</v>
+        <v>2806</v>
       </c>
       <c r="D91" t="s">
         <v>332</v>
@@ -20728,13 +21599,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B92" t="s">
         <v>23</v>
       </c>
       <c r="C92" t="s">
-        <v>2764</v>
+        <v>2807</v>
       </c>
       <c r="D92" t="s">
         <v>332</v>
@@ -20742,13 +21613,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B93" t="s">
         <v>24</v>
       </c>
       <c r="C93" t="s">
-        <v>2764</v>
+        <v>2807</v>
       </c>
       <c r="D93" t="s">
         <v>332</v>
@@ -20756,13 +21627,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>2765</v>
+        <v>2808</v>
       </c>
       <c r="D94" t="s">
         <v>332</v>
@@ -20770,13 +21641,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B95" t="s">
         <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>2766</v>
+        <v>2809</v>
       </c>
       <c r="D95" t="s">
         <v>332</v>
@@ -20784,13 +21655,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>2616</v>
+        <v>2659</v>
       </c>
       <c r="B96" t="s">
         <v>26</v>
       </c>
       <c r="C96" t="s">
-        <v>2767</v>
+        <v>2810</v>
       </c>
       <c r="D96" t="s">
         <v>332</v>
@@ -20798,13 +21669,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>2617</v>
+        <v>2660</v>
       </c>
       <c r="B97" t="s">
         <v>27</v>
       </c>
       <c r="C97" t="s">
-        <v>2768</v>
+        <v>2811</v>
       </c>
       <c r="D97" t="s">
         <v>2105</v>
@@ -20812,13 +21683,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>2617</v>
+        <v>2660</v>
       </c>
       <c r="B98" t="s">
         <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>2769</v>
+        <v>2812</v>
       </c>
       <c r="D98" t="s">
         <v>2105</v>
@@ -20826,13 +21697,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>2617</v>
+        <v>2660</v>
       </c>
       <c r="B99" t="s">
         <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>2770</v>
+        <v>2813</v>
       </c>
       <c r="D99" t="s">
         <v>2105</v>
@@ -20840,13 +21711,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>2617</v>
+        <v>2660</v>
       </c>
       <c r="B100" t="s">
         <v>24</v>
       </c>
       <c r="C100" t="s">
-        <v>2770</v>
+        <v>2813</v>
       </c>
       <c r="D100" t="s">
         <v>2105</v>
@@ -20854,13 +21725,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>2617</v>
+        <v>2660</v>
       </c>
       <c r="B101" t="s">
         <v>26</v>
       </c>
       <c r="C101" t="s">
-        <v>2771</v>
+        <v>2814</v>
       </c>
       <c r="D101" t="s">
         <v>2105</v>
@@ -20868,13 +21739,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B102" t="s">
         <v>27</v>
       </c>
       <c r="C102" t="s">
-        <v>2772</v>
+        <v>2815</v>
       </c>
       <c r="D102" t="s">
         <v>332</v>
@@ -20882,13 +21753,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B103" t="s">
         <v>23</v>
       </c>
       <c r="C103" t="s">
-        <v>2773</v>
+        <v>2816</v>
       </c>
       <c r="D103" t="s">
         <v>332</v>
@@ -20896,13 +21767,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B104" t="s">
         <v>24</v>
       </c>
       <c r="C104" t="s">
-        <v>2773</v>
+        <v>2816</v>
       </c>
       <c r="D104" t="s">
         <v>332</v>
@@ -20910,7 +21781,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B105" t="s">
         <v>22</v>
@@ -20924,13 +21795,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B106" t="s">
         <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>2774</v>
+        <v>2817</v>
       </c>
       <c r="D106" t="s">
         <v>332</v>
@@ -20938,13 +21809,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>2618</v>
+        <v>2661</v>
       </c>
       <c r="B107" t="s">
         <v>26</v>
       </c>
       <c r="C107" t="s">
-        <v>2775</v>
+        <v>2818</v>
       </c>
       <c r="D107" t="s">
         <v>332</v>
@@ -20952,13 +21823,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>2619</v>
+        <v>2662</v>
       </c>
       <c r="B108" t="s">
         <v>27</v>
       </c>
       <c r="C108" t="s">
-        <v>2776</v>
+        <v>2819</v>
       </c>
       <c r="D108" t="s">
         <v>2105</v>
@@ -20966,13 +21837,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>2619</v>
+        <v>2662</v>
       </c>
       <c r="B109" t="s">
         <v>22</v>
       </c>
       <c r="C109" t="s">
-        <v>2777</v>
+        <v>2820</v>
       </c>
       <c r="D109" t="s">
         <v>2105</v>
@@ -20980,13 +21851,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>2619</v>
+        <v>2662</v>
       </c>
       <c r="B110" t="s">
         <v>23</v>
       </c>
       <c r="C110" t="s">
-        <v>2778</v>
+        <v>2821</v>
       </c>
       <c r="D110" t="s">
         <v>2105</v>
@@ -20994,13 +21865,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>2619</v>
+        <v>2662</v>
       </c>
       <c r="B111" t="s">
         <v>24</v>
       </c>
       <c r="C111" t="s">
-        <v>2778</v>
+        <v>2821</v>
       </c>
       <c r="D111" t="s">
         <v>2105</v>
@@ -21008,13 +21879,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>2619</v>
+        <v>2662</v>
       </c>
       <c r="B112" t="s">
         <v>26</v>
       </c>
       <c r="C112" t="s">
-        <v>2779</v>
+        <v>2822</v>
       </c>
       <c r="D112" t="s">
         <v>2105</v>
@@ -21022,13 +21893,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>2620</v>
+        <v>2663</v>
       </c>
       <c r="B113" t="s">
         <v>22</v>
       </c>
       <c r="C113" t="s">
-        <v>2780</v>
+        <v>2823</v>
       </c>
       <c r="D113" t="s">
         <v>332</v>
@@ -21036,13 +21907,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>2621</v>
+        <v>2664</v>
       </c>
       <c r="B114" t="s">
         <v>22</v>
       </c>
       <c r="C114" t="s">
-        <v>2769</v>
+        <v>2812</v>
       </c>
       <c r="D114" t="s">
         <v>2105</v>
@@ -21050,13 +21921,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>2622</v>
+        <v>2665</v>
       </c>
       <c r="B115" t="s">
         <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>2781</v>
+        <v>2824</v>
       </c>
       <c r="D115" t="s">
         <v>332</v>
@@ -21064,13 +21935,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>2623</v>
+        <v>2666</v>
       </c>
       <c r="B116" t="s">
         <v>22</v>
       </c>
       <c r="C116" t="s">
-        <v>2777</v>
+        <v>2820</v>
       </c>
       <c r="D116" t="s">
         <v>2105</v>
@@ -21078,13 +21949,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>2624</v>
+        <v>2667</v>
       </c>
       <c r="B117" t="s">
         <v>27</v>
       </c>
       <c r="C117" t="s">
-        <v>2782</v>
+        <v>2825</v>
       </c>
       <c r="D117" t="s">
         <v>332</v>
@@ -21092,13 +21963,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>2624</v>
+        <v>2667</v>
       </c>
       <c r="B118" t="s">
         <v>23</v>
       </c>
       <c r="C118" t="s">
-        <v>2783</v>
+        <v>2826</v>
       </c>
       <c r="D118" t="s">
         <v>332</v>
@@ -21106,13 +21977,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>2624</v>
+        <v>2667</v>
       </c>
       <c r="B119" t="s">
         <v>24</v>
       </c>
       <c r="C119" t="s">
-        <v>2783</v>
+        <v>2826</v>
       </c>
       <c r="D119" t="s">
         <v>332</v>
@@ -21120,13 +21991,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>2624</v>
+        <v>2667</v>
       </c>
       <c r="B120" t="s">
         <v>26</v>
       </c>
       <c r="C120" t="s">
-        <v>2784</v>
+        <v>2827</v>
       </c>
       <c r="D120" t="s">
         <v>332</v>
@@ -21134,13 +22005,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>2625</v>
+        <v>2668</v>
       </c>
       <c r="B121" t="s">
         <v>27</v>
       </c>
       <c r="C121" t="s">
-        <v>2785</v>
+        <v>2828</v>
       </c>
       <c r="D121" t="s">
         <v>2105</v>
@@ -21148,13 +22019,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>2625</v>
+        <v>2668</v>
       </c>
       <c r="B122" t="s">
         <v>26</v>
       </c>
       <c r="C122" t="s">
-        <v>2786</v>
+        <v>2829</v>
       </c>
       <c r="D122" t="s">
         <v>2105</v>
@@ -21162,13 +22033,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>2626</v>
+        <v>2669</v>
       </c>
       <c r="B123" t="s">
         <v>27</v>
       </c>
       <c r="C123" t="s">
-        <v>2787</v>
+        <v>2830</v>
       </c>
       <c r="D123" t="s">
         <v>332</v>
@@ -21176,13 +22047,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>2626</v>
+        <v>2669</v>
       </c>
       <c r="B124" t="s">
         <v>23</v>
       </c>
       <c r="C124" t="s">
-        <v>2788</v>
+        <v>2831</v>
       </c>
       <c r="D124" t="s">
         <v>332</v>
@@ -21190,13 +22061,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>2626</v>
+        <v>2669</v>
       </c>
       <c r="B125" t="s">
         <v>24</v>
       </c>
       <c r="C125" t="s">
-        <v>2788</v>
+        <v>2831</v>
       </c>
       <c r="D125" t="s">
         <v>332</v>
@@ -21204,13 +22075,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>2627</v>
+        <v>2670</v>
       </c>
       <c r="B126" t="s">
         <v>27</v>
       </c>
       <c r="C126" t="s">
-        <v>2789</v>
+        <v>2832</v>
       </c>
       <c r="D126" t="s">
         <v>2105</v>
@@ -21218,13 +22089,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B127" t="s">
         <v>27</v>
       </c>
       <c r="C127" t="s">
-        <v>2790</v>
+        <v>2833</v>
       </c>
       <c r="D127" t="s">
         <v>332</v>
@@ -21232,13 +22103,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B128" t="s">
         <v>26</v>
       </c>
       <c r="C128" t="s">
-        <v>2791</v>
+        <v>2834</v>
       </c>
       <c r="D128" t="s">
         <v>332</v>
@@ -21246,13 +22117,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B129" t="s">
         <v>23</v>
       </c>
       <c r="C129" t="s">
-        <v>2792</v>
+        <v>2835</v>
       </c>
       <c r="D129" t="s">
         <v>332</v>
@@ -21260,13 +22131,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B130" t="s">
         <v>24</v>
       </c>
       <c r="C130" t="s">
-        <v>2792</v>
+        <v>2835</v>
       </c>
       <c r="D130" t="s">
         <v>332</v>
@@ -21274,13 +22145,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B131" t="s">
         <v>22</v>
       </c>
       <c r="C131" t="s">
-        <v>2793</v>
+        <v>2836</v>
       </c>
       <c r="D131" t="s">
         <v>332</v>
@@ -21288,13 +22159,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B132" t="s">
         <v>22</v>
       </c>
       <c r="C132" t="s">
-        <v>2794</v>
+        <v>2837</v>
       </c>
       <c r="D132" t="s">
         <v>332</v>
@@ -21302,13 +22173,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B133" t="s">
         <v>25</v>
       </c>
       <c r="C133" t="s">
-        <v>2795</v>
+        <v>2838</v>
       </c>
       <c r="D133" t="s">
         <v>332</v>
@@ -21316,13 +22187,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>2628</v>
+        <v>2671</v>
       </c>
       <c r="B134" t="s">
         <v>1600</v>
       </c>
       <c r="C134" t="s">
-        <v>2796</v>
+        <v>2839</v>
       </c>
       <c r="D134" t="s">
         <v>332</v>
@@ -21330,13 +22201,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>2629</v>
+        <v>2672</v>
       </c>
       <c r="B135" t="s">
         <v>26</v>
       </c>
       <c r="C135" t="s">
-        <v>2797</v>
+        <v>2840</v>
       </c>
       <c r="D135" t="s">
         <v>2105</v>
@@ -21344,13 +22215,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>2629</v>
+        <v>2672</v>
       </c>
       <c r="B136" t="s">
         <v>23</v>
       </c>
       <c r="C136" t="s">
-        <v>2798</v>
+        <v>2841</v>
       </c>
       <c r="D136" t="s">
         <v>2105</v>
@@ -21358,13 +22229,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>2629</v>
+        <v>2672</v>
       </c>
       <c r="B137" t="s">
         <v>24</v>
       </c>
       <c r="C137" t="s">
-        <v>2798</v>
+        <v>2841</v>
       </c>
       <c r="D137" t="s">
         <v>2105</v>
@@ -21372,13 +22243,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>2629</v>
+        <v>2672</v>
       </c>
       <c r="B138" t="s">
         <v>27</v>
       </c>
       <c r="C138" t="s">
-        <v>2797</v>
+        <v>2840</v>
       </c>
       <c r="D138" t="s">
         <v>2105</v>
@@ -21386,13 +22257,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>2629</v>
+        <v>2672</v>
       </c>
       <c r="B139" t="s">
         <v>1600</v>
       </c>
       <c r="C139" t="s">
-        <v>2799</v>
+        <v>2842</v>
       </c>
       <c r="D139" t="s">
         <v>2105</v>
@@ -21400,13 +22271,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>2630</v>
+        <v>2673</v>
       </c>
       <c r="B140" t="s">
         <v>22</v>
       </c>
       <c r="C140" t="s">
-        <v>2800</v>
+        <v>2843</v>
       </c>
       <c r="D140" t="s">
         <v>332</v>
@@ -21414,13 +22285,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>2631</v>
+        <v>2674</v>
       </c>
       <c r="B141" t="s">
         <v>22</v>
       </c>
       <c r="C141" t="s">
-        <v>2801</v>
+        <v>2844</v>
       </c>
       <c r="D141" t="s">
         <v>332</v>
@@ -21428,13 +22299,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>2632</v>
+        <v>2675</v>
       </c>
       <c r="B142" t="s">
         <v>22</v>
       </c>
       <c r="C142" t="s">
-        <v>2802</v>
+        <v>2845</v>
       </c>
       <c r="D142" t="s">
         <v>332</v>
@@ -21442,13 +22313,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>2633</v>
+        <v>2676</v>
       </c>
       <c r="B143" t="s">
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>2803</v>
+        <v>2846</v>
       </c>
       <c r="D143" t="s">
         <v>332</v>
@@ -21456,13 +22327,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>2634</v>
+        <v>2677</v>
       </c>
       <c r="B144" t="s">
         <v>22</v>
       </c>
       <c r="C144" t="s">
-        <v>2804</v>
+        <v>2847</v>
       </c>
       <c r="D144" t="s">
         <v>332</v>
@@ -21470,13 +22341,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>2635</v>
+        <v>2678</v>
       </c>
       <c r="B145" t="s">
         <v>1600</v>
       </c>
       <c r="C145" t="s">
-        <v>2805</v>
+        <v>2848</v>
       </c>
       <c r="D145" t="s">
         <v>332</v>
@@ -21484,13 +22355,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>2636</v>
+        <v>2679</v>
       </c>
       <c r="B146" t="s">
         <v>1600</v>
       </c>
       <c r="C146" t="s">
-        <v>2806</v>
+        <v>2849</v>
       </c>
       <c r="D146" t="s">
         <v>2105</v>
@@ -21498,13 +22369,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B147" t="s">
         <v>27</v>
       </c>
       <c r="C147" t="s">
-        <v>2807</v>
+        <v>2850</v>
       </c>
       <c r="D147" t="s">
         <v>332</v>
@@ -21512,13 +22383,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B148" t="s">
         <v>26</v>
       </c>
       <c r="C148" t="s">
-        <v>2808</v>
+        <v>2851</v>
       </c>
       <c r="D148" t="s">
         <v>332</v>
@@ -21526,13 +22397,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B149" t="s">
         <v>23</v>
       </c>
       <c r="C149" t="s">
-        <v>2809</v>
+        <v>2852</v>
       </c>
       <c r="D149" t="s">
         <v>332</v>
@@ -21540,13 +22411,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B150" t="s">
         <v>24</v>
       </c>
       <c r="C150" t="s">
-        <v>2809</v>
+        <v>2852</v>
       </c>
       <c r="D150" t="s">
         <v>332</v>
@@ -21554,13 +22425,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B151" t="s">
         <v>22</v>
       </c>
       <c r="C151" t="s">
-        <v>2810</v>
+        <v>2853</v>
       </c>
       <c r="D151" t="s">
         <v>332</v>
@@ -21568,13 +22439,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>2637</v>
+        <v>2680</v>
       </c>
       <c r="B152" t="s">
         <v>25</v>
       </c>
       <c r="C152" t="s">
-        <v>2810</v>
+        <v>2853</v>
       </c>
       <c r="D152" t="s">
         <v>332</v>
@@ -21582,13 +22453,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>2638</v>
+        <v>2681</v>
       </c>
       <c r="B153" t="s">
         <v>26</v>
       </c>
       <c r="C153" t="s">
-        <v>2811</v>
+        <v>2854</v>
       </c>
       <c r="D153" t="s">
         <v>2105</v>
@@ -21596,13 +22467,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>2638</v>
+        <v>2681</v>
       </c>
       <c r="B154" t="s">
         <v>23</v>
       </c>
       <c r="C154" t="s">
-        <v>2812</v>
+        <v>2855</v>
       </c>
       <c r="D154" t="s">
         <v>2105</v>
@@ -21610,13 +22481,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>2638</v>
+        <v>2681</v>
       </c>
       <c r="B155" t="s">
         <v>24</v>
       </c>
       <c r="C155" t="s">
-        <v>2812</v>
+        <v>2855</v>
       </c>
       <c r="D155" t="s">
         <v>2105</v>
@@ -21624,13 +22495,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B156" t="s">
         <v>27</v>
       </c>
       <c r="C156" t="s">
-        <v>2813</v>
+        <v>2856</v>
       </c>
       <c r="D156" t="s">
         <v>332</v>
@@ -21638,13 +22509,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B157" t="s">
         <v>26</v>
       </c>
       <c r="C157" t="s">
-        <v>2814</v>
+        <v>2857</v>
       </c>
       <c r="D157" t="s">
         <v>332</v>
@@ -21652,13 +22523,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B158" t="s">
         <v>23</v>
       </c>
       <c r="C158" t="s">
-        <v>2815</v>
+        <v>2858</v>
       </c>
       <c r="D158" t="s">
         <v>332</v>
@@ -21666,13 +22537,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B159" t="s">
         <v>24</v>
       </c>
       <c r="C159" t="s">
-        <v>2815</v>
+        <v>2858</v>
       </c>
       <c r="D159" t="s">
         <v>332</v>
@@ -21680,13 +22551,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B160" t="s">
         <v>22</v>
       </c>
       <c r="C160" t="s">
-        <v>2816</v>
+        <v>2859</v>
       </c>
       <c r="D160" t="s">
         <v>332</v>
@@ -21694,13 +22565,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>2639</v>
+        <v>2682</v>
       </c>
       <c r="B161" t="s">
         <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>2816</v>
+        <v>2859</v>
       </c>
       <c r="D161" t="s">
         <v>332</v>
@@ -21708,13 +22579,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>2640</v>
+        <v>2683</v>
       </c>
       <c r="B162" t="s">
         <v>26</v>
       </c>
       <c r="C162" t="s">
-        <v>2817</v>
+        <v>2860</v>
       </c>
       <c r="D162" t="s">
         <v>2105</v>
@@ -21722,13 +22593,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>2640</v>
+        <v>2683</v>
       </c>
       <c r="B163" t="s">
         <v>23</v>
       </c>
       <c r="C163" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
       <c r="D163" t="s">
         <v>2105</v>
@@ -21736,13 +22607,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>2640</v>
+        <v>2683</v>
       </c>
       <c r="B164" t="s">
         <v>24</v>
       </c>
       <c r="C164" t="s">
-        <v>2818</v>
+        <v>2861</v>
       </c>
       <c r="D164" t="s">
         <v>2105</v>
@@ -21750,13 +22621,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>2641</v>
+        <v>2684</v>
       </c>
       <c r="B165" t="s">
         <v>27</v>
       </c>
       <c r="C165" t="s">
-        <v>2819</v>
+        <v>2862</v>
       </c>
       <c r="D165" t="s">
         <v>332</v>
@@ -21764,13 +22635,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>2641</v>
+        <v>2684</v>
       </c>
       <c r="B166" t="s">
         <v>23</v>
       </c>
       <c r="C166" t="s">
-        <v>2820</v>
+        <v>2863</v>
       </c>
       <c r="D166" t="s">
         <v>332</v>
@@ -21778,13 +22649,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>2641</v>
+        <v>2684</v>
       </c>
       <c r="B167" t="s">
         <v>24</v>
       </c>
       <c r="C167" t="s">
-        <v>2820</v>
+        <v>2863</v>
       </c>
       <c r="D167" t="s">
         <v>332</v>
@@ -21792,13 +22663,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>2641</v>
+        <v>2684</v>
       </c>
       <c r="B168" t="s">
         <v>22</v>
       </c>
       <c r="C168" t="s">
-        <v>2821</v>
+        <v>2864</v>
       </c>
       <c r="D168" t="s">
         <v>332</v>
@@ -21806,13 +22677,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>2641</v>
+        <v>2684</v>
       </c>
       <c r="B169" t="s">
         <v>25</v>
       </c>
       <c r="C169" t="s">
-        <v>2821</v>
+        <v>2864</v>
       </c>
       <c r="D169" t="s">
         <v>332</v>
@@ -21820,13 +22691,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
-        <v>2642</v>
+        <v>2685</v>
       </c>
       <c r="B170" t="s">
         <v>23</v>
       </c>
       <c r="C170" t="s">
-        <v>2822</v>
+        <v>2865</v>
       </c>
       <c r="D170" t="s">
         <v>2105</v>
@@ -21834,13 +22705,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>2642</v>
+        <v>2685</v>
       </c>
       <c r="B171" t="s">
         <v>24</v>
       </c>
       <c r="C171" t="s">
-        <v>2822</v>
+        <v>2865</v>
       </c>
       <c r="D171" t="s">
         <v>2105</v>
@@ -21848,13 +22719,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B172" t="s">
         <v>27</v>
       </c>
       <c r="C172" t="s">
-        <v>2823</v>
+        <v>2866</v>
       </c>
       <c r="D172" t="s">
         <v>332</v>
@@ -21862,13 +22733,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B173" t="s">
         <v>26</v>
       </c>
       <c r="C173" t="s">
-        <v>2824</v>
+        <v>2867</v>
       </c>
       <c r="D173" t="s">
         <v>332</v>
@@ -21876,13 +22747,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B174" t="s">
         <v>23</v>
       </c>
       <c r="C174" t="s">
-        <v>2825</v>
+        <v>2868</v>
       </c>
       <c r="D174" t="s">
         <v>332</v>
@@ -21890,13 +22761,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B175" t="s">
         <v>24</v>
       </c>
       <c r="C175" t="s">
-        <v>2825</v>
+        <v>2868</v>
       </c>
       <c r="D175" t="s">
         <v>332</v>
@@ -21904,13 +22775,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B176" t="s">
         <v>22</v>
       </c>
       <c r="C176" t="s">
-        <v>2826</v>
+        <v>2869</v>
       </c>
       <c r="D176" t="s">
         <v>332</v>
@@ -21918,13 +22789,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>2643</v>
+        <v>2686</v>
       </c>
       <c r="B177" t="s">
         <v>25</v>
       </c>
       <c r="C177" t="s">
-        <v>2826</v>
+        <v>2869</v>
       </c>
       <c r="D177" t="s">
         <v>332</v>
@@ -21932,13 +22803,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>2644</v>
+        <v>2687</v>
       </c>
       <c r="B178" t="s">
         <v>26</v>
       </c>
       <c r="C178" t="s">
-        <v>2827</v>
+        <v>2870</v>
       </c>
       <c r="D178" t="s">
         <v>2105</v>
@@ -21946,13 +22817,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>2644</v>
+        <v>2687</v>
       </c>
       <c r="B179" t="s">
         <v>23</v>
       </c>
       <c r="C179" t="s">
-        <v>2828</v>
+        <v>2871</v>
       </c>
       <c r="D179" t="s">
         <v>2105</v>
@@ -21960,13 +22831,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>2644</v>
+        <v>2687</v>
       </c>
       <c r="B180" t="s">
         <v>24</v>
       </c>
       <c r="C180" t="s">
-        <v>2828</v>
+        <v>2871</v>
       </c>
       <c r="D180" t="s">
         <v>2105</v>
@@ -21974,13 +22845,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B181" t="s">
         <v>27</v>
       </c>
       <c r="C181" t="s">
-        <v>2829</v>
+        <v>2872</v>
       </c>
       <c r="D181" t="s">
         <v>332</v>
@@ -21988,13 +22859,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B182" t="s">
         <v>26</v>
       </c>
       <c r="C182" t="s">
-        <v>2830</v>
+        <v>2873</v>
       </c>
       <c r="D182" t="s">
         <v>332</v>
@@ -22002,13 +22873,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B183" t="s">
         <v>23</v>
       </c>
       <c r="C183" t="s">
-        <v>2831</v>
+        <v>2874</v>
       </c>
       <c r="D183" t="s">
         <v>332</v>
@@ -22016,13 +22887,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B184" t="s">
         <v>24</v>
       </c>
       <c r="C184" t="s">
-        <v>2831</v>
+        <v>2874</v>
       </c>
       <c r="D184" t="s">
         <v>332</v>
@@ -22030,13 +22901,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B185" t="s">
         <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>2832</v>
+        <v>2875</v>
       </c>
       <c r="D185" t="s">
         <v>332</v>
@@ -22044,13 +22915,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B186" t="s">
         <v>25</v>
       </c>
       <c r="C186" t="s">
-        <v>2832</v>
+        <v>2875</v>
       </c>
       <c r="D186" t="s">
         <v>332</v>
@@ -22058,13 +22929,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>2645</v>
+        <v>2688</v>
       </c>
       <c r="B187" t="s">
         <v>1600</v>
       </c>
       <c r="C187" t="s">
-        <v>2832</v>
+        <v>2875</v>
       </c>
       <c r="D187" t="s">
         <v>332</v>
@@ -22072,13 +22943,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>2646</v>
+        <v>2689</v>
       </c>
       <c r="B188" t="s">
         <v>26</v>
       </c>
       <c r="C188" t="s">
-        <v>2833</v>
+        <v>2876</v>
       </c>
       <c r="D188" t="s">
         <v>2105</v>
@@ -22086,13 +22957,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>2646</v>
+        <v>2689</v>
       </c>
       <c r="B189" t="s">
         <v>23</v>
       </c>
       <c r="C189" t="s">
-        <v>2834</v>
+        <v>2877</v>
       </c>
       <c r="D189" t="s">
         <v>2105</v>
@@ -22100,13 +22971,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>2646</v>
+        <v>2689</v>
       </c>
       <c r="B190" t="s">
         <v>24</v>
       </c>
       <c r="C190" t="s">
-        <v>2834</v>
+        <v>2877</v>
       </c>
       <c r="D190" t="s">
         <v>2105</v>
@@ -22114,13 +22985,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>2646</v>
+        <v>2689</v>
       </c>
       <c r="B191" t="s">
         <v>1600</v>
       </c>
       <c r="C191" t="s">
-        <v>2835</v>
+        <v>2878</v>
       </c>
       <c r="D191" t="s">
         <v>2105</v>
@@ -22128,13 +22999,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>2647</v>
+        <v>2690</v>
       </c>
       <c r="B192" t="s">
         <v>23</v>
       </c>
       <c r="C192" t="s">
-        <v>2836</v>
+        <v>2879</v>
       </c>
       <c r="D192" t="s">
         <v>332</v>
@@ -22142,13 +23013,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>2647</v>
+        <v>2690</v>
       </c>
       <c r="B193" t="s">
         <v>24</v>
       </c>
       <c r="C193" t="s">
-        <v>2836</v>
+        <v>2879</v>
       </c>
       <c r="D193" t="s">
         <v>332</v>
@@ -22156,13 +23027,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>2647</v>
+        <v>2690</v>
       </c>
       <c r="B194" t="s">
         <v>22</v>
       </c>
       <c r="C194" t="s">
-        <v>2837</v>
+        <v>2880</v>
       </c>
       <c r="D194" t="s">
         <v>332</v>
@@ -22170,13 +23041,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>2647</v>
+        <v>2690</v>
       </c>
       <c r="B195" t="s">
         <v>25</v>
       </c>
       <c r="C195" t="s">
-        <v>2837</v>
+        <v>2880</v>
       </c>
       <c r="D195" t="s">
         <v>332</v>
@@ -22184,13 +23055,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>2647</v>
+        <v>2690</v>
       </c>
       <c r="B196" t="s">
         <v>1600</v>
       </c>
       <c r="C196" t="s">
-        <v>2837</v>
+        <v>2880</v>
       </c>
       <c r="D196" t="s">
         <v>332</v>
@@ -22198,13 +23069,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>2648</v>
+        <v>2691</v>
       </c>
       <c r="B197" t="s">
         <v>23</v>
       </c>
       <c r="C197" t="s">
-        <v>2838</v>
+        <v>2881</v>
       </c>
       <c r="D197" t="s">
         <v>2105</v>
@@ -22212,13 +23083,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>2648</v>
+        <v>2691</v>
       </c>
       <c r="B198" t="s">
         <v>24</v>
       </c>
       <c r="C198" t="s">
-        <v>2838</v>
+        <v>2881</v>
       </c>
       <c r="D198" t="s">
         <v>2105</v>
@@ -22226,13 +23097,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>2648</v>
+        <v>2691</v>
       </c>
       <c r="B199" t="s">
         <v>1600</v>
       </c>
       <c r="C199" t="s">
-        <v>2839</v>
+        <v>2882</v>
       </c>
       <c r="D199" t="s">
         <v>2105</v>
@@ -22240,13 +23111,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>2649</v>
+        <v>2692</v>
       </c>
       <c r="B200" t="s">
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>2840</v>
+        <v>2883</v>
       </c>
       <c r="D200" t="s">
         <v>332</v>
@@ -22254,13 +23125,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>2650</v>
+        <v>2693</v>
       </c>
       <c r="B201" t="s">
         <v>22</v>
       </c>
       <c r="C201" t="s">
-        <v>2841</v>
+        <v>2884</v>
       </c>
       <c r="D201" t="s">
         <v>332</v>
@@ -22268,13 +23139,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>2651</v>
+        <v>2694</v>
       </c>
       <c r="B202" t="s">
         <v>27</v>
       </c>
       <c r="C202" t="s">
-        <v>2842</v>
+        <v>2885</v>
       </c>
       <c r="D202" t="s">
         <v>332</v>
@@ -22282,13 +23153,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>2651</v>
+        <v>2694</v>
       </c>
       <c r="B203" t="s">
         <v>23</v>
       </c>
       <c r="C203" t="s">
-        <v>2843</v>
+        <v>2886</v>
       </c>
       <c r="D203" t="s">
         <v>332</v>
@@ -22296,13 +23167,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>2651</v>
+        <v>2694</v>
       </c>
       <c r="B204" t="s">
         <v>24</v>
       </c>
       <c r="C204" t="s">
-        <v>2843</v>
+        <v>2886</v>
       </c>
       <c r="D204" t="s">
         <v>332</v>
@@ -22310,13 +23181,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>2651</v>
+        <v>2694</v>
       </c>
       <c r="B205" t="s">
         <v>22</v>
       </c>
       <c r="C205" t="s">
-        <v>2844</v>
+        <v>2887</v>
       </c>
       <c r="D205" t="s">
         <v>332</v>
@@ -22324,13 +23195,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>2651</v>
+        <v>2694</v>
       </c>
       <c r="B206" t="s">
         <v>26</v>
       </c>
       <c r="C206" t="s">
-        <v>2845</v>
+        <v>2888</v>
       </c>
       <c r="D206" t="s">
         <v>332</v>
@@ -22338,13 +23209,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>2652</v>
+        <v>2695</v>
       </c>
       <c r="B207" t="s">
         <v>27</v>
       </c>
       <c r="C207" t="s">
-        <v>2768</v>
+        <v>2811</v>
       </c>
       <c r="D207" t="s">
         <v>2105</v>
@@ -22352,13 +23223,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>2652</v>
+        <v>2695</v>
       </c>
       <c r="B208" t="s">
         <v>23</v>
       </c>
       <c r="C208" t="s">
-        <v>2846</v>
+        <v>2889</v>
       </c>
       <c r="D208" t="s">
         <v>2105</v>
@@ -22366,13 +23237,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>2652</v>
+        <v>2695</v>
       </c>
       <c r="B209" t="s">
         <v>24</v>
       </c>
       <c r="C209" t="s">
-        <v>2846</v>
+        <v>2889</v>
       </c>
       <c r="D209" t="s">
         <v>2105</v>
@@ -22380,13 +23251,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>2652</v>
+        <v>2695</v>
       </c>
       <c r="B210" t="s">
         <v>22</v>
       </c>
       <c r="C210" t="s">
-        <v>2847</v>
+        <v>2890</v>
       </c>
       <c r="D210" t="s">
         <v>2105</v>
@@ -22394,13 +23265,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>2652</v>
+        <v>2695</v>
       </c>
       <c r="B211" t="s">
         <v>26</v>
       </c>
       <c r="C211" t="s">
-        <v>2848</v>
+        <v>2891</v>
       </c>
       <c r="D211" t="s">
         <v>2105</v>
@@ -22408,13 +23279,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>2653</v>
+        <v>2696</v>
       </c>
       <c r="B212" t="s">
         <v>27</v>
       </c>
       <c r="C212" t="s">
-        <v>2849</v>
+        <v>2892</v>
       </c>
       <c r="D212" t="s">
         <v>332</v>
@@ -22422,13 +23293,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>2653</v>
+        <v>2696</v>
       </c>
       <c r="B213" t="s">
         <v>22</v>
       </c>
       <c r="C213" t="s">
-        <v>2850</v>
+        <v>2893</v>
       </c>
       <c r="D213" t="s">
         <v>332</v>
@@ -22436,13 +23307,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>2654</v>
+        <v>2697</v>
       </c>
       <c r="B214" t="s">
         <v>27</v>
       </c>
       <c r="C214" t="s">
-        <v>2776</v>
+        <v>2819</v>
       </c>
       <c r="D214" t="s">
         <v>2105</v>
@@ -22450,13 +23321,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>2654</v>
+        <v>2697</v>
       </c>
       <c r="B215" t="s">
         <v>22</v>
       </c>
       <c r="C215" t="s">
-        <v>2851</v>
+        <v>2894</v>
       </c>
       <c r="D215" t="s">
         <v>2105</v>
@@ -22464,13 +23335,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B216" t="s">
         <v>23</v>
       </c>
       <c r="C216" t="s">
-        <v>2852</v>
+        <v>2895</v>
       </c>
       <c r="D216" t="s">
         <v>332</v>
@@ -22478,13 +23349,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B217" t="s">
         <v>24</v>
       </c>
       <c r="C217" t="s">
-        <v>2852</v>
+        <v>2895</v>
       </c>
       <c r="D217" t="s">
         <v>332</v>
@@ -22492,13 +23363,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B218" t="s">
         <v>22</v>
       </c>
       <c r="C218" t="s">
-        <v>2853</v>
+        <v>2896</v>
       </c>
       <c r="D218" t="s">
         <v>332</v>
@@ -22506,13 +23377,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B219" t="s">
         <v>25</v>
       </c>
       <c r="C219" t="s">
-        <v>2854</v>
+        <v>2897</v>
       </c>
       <c r="D219" t="s">
         <v>332</v>
@@ -22520,13 +23391,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B220" t="s">
         <v>1600</v>
       </c>
       <c r="C220" t="s">
-        <v>2855</v>
+        <v>2898</v>
       </c>
       <c r="D220" t="s">
         <v>332</v>
@@ -22534,13 +23405,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>2655</v>
+        <v>2698</v>
       </c>
       <c r="B221" t="s">
         <v>26</v>
       </c>
       <c r="C221" t="s">
-        <v>2856</v>
+        <v>2899</v>
       </c>
       <c r="D221" t="s">
         <v>332</v>
@@ -22548,13 +23419,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>2656</v>
+        <v>2699</v>
       </c>
       <c r="B222" t="s">
         <v>23</v>
       </c>
       <c r="C222" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D222" t="s">
         <v>2105</v>
@@ -22562,13 +23433,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>2656</v>
+        <v>2699</v>
       </c>
       <c r="B223" t="s">
         <v>24</v>
       </c>
       <c r="C223" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D223" t="s">
         <v>2105</v>
@@ -22576,13 +23447,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>2656</v>
+        <v>2699</v>
       </c>
       <c r="B224" t="s">
         <v>22</v>
       </c>
       <c r="C224" t="s">
-        <v>2858</v>
+        <v>2901</v>
       </c>
       <c r="D224" t="s">
         <v>2105</v>
@@ -22590,13 +23461,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>2656</v>
+        <v>2699</v>
       </c>
       <c r="B225" t="s">
         <v>26</v>
       </c>
       <c r="C225" t="s">
-        <v>2859</v>
+        <v>2902</v>
       </c>
       <c r="D225" t="s">
         <v>2105</v>
@@ -22604,7 +23475,7 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>2657</v>
+        <v>2700</v>
       </c>
       <c r="B226" t="s">
         <v>22</v>
@@ -22618,13 +23489,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>2657</v>
+        <v>2700</v>
       </c>
       <c r="B227" t="s">
         <v>25</v>
       </c>
       <c r="C227" t="s">
-        <v>2860</v>
+        <v>2903</v>
       </c>
       <c r="D227" t="s">
         <v>332</v>
@@ -22632,13 +23503,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>2657</v>
+        <v>2700</v>
       </c>
       <c r="B228" t="s">
         <v>26</v>
       </c>
       <c r="C228" t="s">
-        <v>2861</v>
+        <v>2904</v>
       </c>
       <c r="D228" t="s">
         <v>332</v>
@@ -22646,13 +23517,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>2658</v>
+        <v>2701</v>
       </c>
       <c r="B229" t="s">
         <v>22</v>
       </c>
       <c r="C229" t="s">
-        <v>2862</v>
+        <v>2905</v>
       </c>
       <c r="D229" t="s">
         <v>2105</v>
@@ -22660,13 +23531,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>2658</v>
+        <v>2701</v>
       </c>
       <c r="B230" t="s">
         <v>26</v>
       </c>
       <c r="C230" t="s">
-        <v>2863</v>
+        <v>2906</v>
       </c>
       <c r="D230" t="s">
         <v>2105</v>
@@ -22674,13 +23545,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>2659</v>
+        <v>2702</v>
       </c>
       <c r="B231" t="s">
         <v>23</v>
       </c>
       <c r="C231" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D231" t="s">
         <v>2105</v>
@@ -22688,13 +23559,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>2659</v>
+        <v>2702</v>
       </c>
       <c r="B232" t="s">
         <v>24</v>
       </c>
       <c r="C232" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D232" t="s">
         <v>2105</v>
@@ -22702,13 +23573,13 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>2660</v>
+        <v>2703</v>
       </c>
       <c r="B233" t="s">
         <v>22</v>
       </c>
       <c r="C233" t="s">
-        <v>2864</v>
+        <v>2907</v>
       </c>
       <c r="D233" t="s">
         <v>332</v>
@@ -22716,13 +23587,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>2661</v>
+        <v>2704</v>
       </c>
       <c r="B234" t="s">
         <v>23</v>
       </c>
       <c r="C234" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D234" t="s">
         <v>2105</v>
@@ -22730,13 +23601,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>2661</v>
+        <v>2704</v>
       </c>
       <c r="B235" t="s">
         <v>24</v>
       </c>
       <c r="C235" t="s">
-        <v>2857</v>
+        <v>2900</v>
       </c>
       <c r="D235" t="s">
         <v>2105</v>
@@ -22744,13 +23615,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>2661</v>
+        <v>2704</v>
       </c>
       <c r="B236" t="s">
         <v>22</v>
       </c>
       <c r="C236" t="s">
-        <v>2865</v>
+        <v>2908</v>
       </c>
       <c r="D236" t="s">
         <v>2105</v>
@@ -22758,13 +23629,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>2662</v>
+        <v>2705</v>
       </c>
       <c r="B237" t="s">
         <v>22</v>
       </c>
       <c r="C237" t="s">
-        <v>2866</v>
+        <v>2909</v>
       </c>
       <c r="D237" t="s">
         <v>332</v>
@@ -22772,13 +23643,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>2663</v>
+        <v>2706</v>
       </c>
       <c r="B238" t="s">
         <v>22</v>
       </c>
       <c r="C238" t="s">
-        <v>2867</v>
+        <v>2910</v>
       </c>
       <c r="D238" t="s">
         <v>2105</v>
@@ -22786,13 +23657,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>2664</v>
+        <v>2707</v>
       </c>
       <c r="B239" t="s">
         <v>22</v>
       </c>
       <c r="C239" t="s">
-        <v>2868</v>
+        <v>2911</v>
       </c>
       <c r="D239" t="s">
         <v>332</v>
@@ -22800,13 +23671,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>2664</v>
+        <v>2707</v>
       </c>
       <c r="B240" t="s">
         <v>26</v>
       </c>
       <c r="C240" t="s">
-        <v>2869</v>
+        <v>2912</v>
       </c>
       <c r="D240" t="s">
         <v>332</v>
@@ -22814,13 +23685,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>2665</v>
+        <v>2708</v>
       </c>
       <c r="B241" t="s">
         <v>22</v>
       </c>
       <c r="C241" t="s">
-        <v>2870</v>
+        <v>2913</v>
       </c>
       <c r="D241" t="s">
         <v>2105</v>
@@ -22828,13 +23699,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>2665</v>
+        <v>2708</v>
       </c>
       <c r="B242" t="s">
         <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>2871</v>
+        <v>2914</v>
       </c>
       <c r="D242" t="s">
         <v>2105</v>
@@ -22842,13 +23713,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>2666</v>
+        <v>2709</v>
       </c>
       <c r="B243" t="s">
         <v>22</v>
       </c>
       <c r="C243" t="s">
-        <v>2872</v>
+        <v>2915</v>
       </c>
       <c r="D243" t="s">
         <v>332</v>
@@ -22856,13 +23727,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>2667</v>
+        <v>2710</v>
       </c>
       <c r="B244" t="s">
         <v>22</v>
       </c>
       <c r="C244" t="s">
-        <v>2873</v>
+        <v>2916</v>
       </c>
       <c r="D244" t="s">
         <v>2105</v>
@@ -22870,13 +23741,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>2668</v>
+        <v>2711</v>
       </c>
       <c r="B245" t="s">
         <v>23</v>
       </c>
       <c r="C245" t="s">
-        <v>2874</v>
+        <v>2917</v>
       </c>
       <c r="D245" t="s">
         <v>332</v>
@@ -22884,13 +23755,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>2668</v>
+        <v>2711</v>
       </c>
       <c r="B246" t="s">
         <v>24</v>
       </c>
       <c r="C246" t="s">
-        <v>2874</v>
+        <v>2917</v>
       </c>
       <c r="D246" t="s">
         <v>332</v>
@@ -22898,13 +23769,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>2668</v>
+        <v>2711</v>
       </c>
       <c r="B247" t="s">
         <v>22</v>
       </c>
       <c r="C247" t="s">
-        <v>2875</v>
+        <v>2918</v>
       </c>
       <c r="D247" t="s">
         <v>332</v>
@@ -22912,13 +23783,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>2668</v>
+        <v>2711</v>
       </c>
       <c r="B248" t="s">
         <v>1600</v>
       </c>
       <c r="C248" t="s">
-        <v>2876</v>
+        <v>2919</v>
       </c>
       <c r="D248" t="s">
         <v>332</v>
@@ -22926,13 +23797,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>2668</v>
+        <v>2711</v>
       </c>
       <c r="B249" t="s">
         <v>26</v>
       </c>
       <c r="C249" t="s">
-        <v>2877</v>
+        <v>2920</v>
       </c>
       <c r="D249" t="s">
         <v>332</v>
@@ -22940,13 +23811,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" t="s">
-        <v>2669</v>
+        <v>2712</v>
       </c>
       <c r="B250" t="s">
         <v>23</v>
       </c>
       <c r="C250" t="s">
-        <v>2878</v>
+        <v>2921</v>
       </c>
       <c r="D250" t="s">
         <v>2105</v>
@@ -22954,13 +23825,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" t="s">
-        <v>2669</v>
+        <v>2712</v>
       </c>
       <c r="B251" t="s">
         <v>24</v>
       </c>
       <c r="C251" t="s">
-        <v>2878</v>
+        <v>2921</v>
       </c>
       <c r="D251" t="s">
         <v>2105</v>
@@ -22968,13 +23839,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" t="s">
-        <v>2669</v>
+        <v>2712</v>
       </c>
       <c r="B252" t="s">
         <v>22</v>
       </c>
       <c r="C252" t="s">
-        <v>2879</v>
+        <v>2922</v>
       </c>
       <c r="D252" t="s">
         <v>2105</v>
@@ -22982,13 +23853,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" t="s">
-        <v>2669</v>
+        <v>2712</v>
       </c>
       <c r="B253" t="s">
         <v>26</v>
       </c>
       <c r="C253" t="s">
-        <v>2880</v>
+        <v>2923</v>
       </c>
       <c r="D253" t="s">
         <v>2105</v>
@@ -22996,13 +23867,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" t="s">
-        <v>2670</v>
+        <v>2713</v>
       </c>
       <c r="B254" t="s">
         <v>22</v>
       </c>
       <c r="C254" t="s">
-        <v>2881</v>
+        <v>2924</v>
       </c>
       <c r="D254" t="s">
         <v>332</v>
@@ -23010,13 +23881,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" t="s">
-        <v>2671</v>
+        <v>2714</v>
       </c>
       <c r="B255" t="s">
         <v>22</v>
       </c>
       <c r="C255" t="s">
-        <v>2882</v>
+        <v>2925</v>
       </c>
       <c r="D255" t="s">
         <v>2105</v>
@@ -23024,13 +23895,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" t="s">
-        <v>2672</v>
+        <v>2715</v>
       </c>
       <c r="B256" t="s">
         <v>22</v>
       </c>
       <c r="C256" t="s">
-        <v>2883</v>
+        <v>2926</v>
       </c>
       <c r="D256" t="s">
         <v>332</v>
@@ -23038,13 +23909,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" t="s">
-        <v>2672</v>
+        <v>2715</v>
       </c>
       <c r="B257" t="s">
         <v>25</v>
       </c>
       <c r="C257" t="s">
-        <v>2884</v>
+        <v>2927</v>
       </c>
       <c r="D257" t="s">
         <v>332</v>
@@ -23052,13 +23923,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" t="s">
-        <v>2673</v>
+        <v>2716</v>
       </c>
       <c r="B258" t="s">
         <v>22</v>
       </c>
       <c r="C258" t="s">
-        <v>2885</v>
+        <v>2928</v>
       </c>
       <c r="D258" t="s">
         <v>2105</v>
@@ -23066,13 +23937,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" t="s">
-        <v>2674</v>
+        <v>2717</v>
       </c>
       <c r="B259" t="s">
         <v>22</v>
       </c>
       <c r="C259" t="s">
-        <v>2886</v>
+        <v>2929</v>
       </c>
       <c r="D259" t="s">
         <v>332</v>
@@ -23080,13 +23951,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" t="s">
-        <v>2675</v>
+        <v>2718</v>
       </c>
       <c r="B260" t="s">
         <v>22</v>
       </c>
       <c r="C260" t="s">
-        <v>2887</v>
+        <v>2930</v>
       </c>
       <c r="D260" t="s">
         <v>2105</v>
@@ -23094,13 +23965,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" t="s">
-        <v>2676</v>
+        <v>2719</v>
       </c>
       <c r="B261" t="s">
         <v>22</v>
       </c>
       <c r="C261" t="s">
-        <v>2888</v>
+        <v>2931</v>
       </c>
       <c r="D261" t="s">
         <v>332</v>
@@ -23108,13 +23979,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" t="s">
-        <v>2676</v>
+        <v>2719</v>
       </c>
       <c r="B262" t="s">
         <v>25</v>
       </c>
       <c r="C262" t="s">
-        <v>2889</v>
+        <v>2932</v>
       </c>
       <c r="D262" t="s">
         <v>332</v>
@@ -23122,13 +23993,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" t="s">
-        <v>2677</v>
+        <v>2720</v>
       </c>
       <c r="B263" t="s">
         <v>22</v>
       </c>
       <c r="C263" t="s">
-        <v>2890</v>
+        <v>2933</v>
       </c>
       <c r="D263" t="s">
         <v>2105</v>
@@ -23136,13 +24007,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" t="s">
-        <v>2678</v>
+        <v>2721</v>
       </c>
       <c r="B264" t="s">
         <v>22</v>
       </c>
       <c r="C264" t="s">
-        <v>2891</v>
+        <v>2934</v>
       </c>
       <c r="D264" t="s">
         <v>332</v>
@@ -23150,13 +24021,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" t="s">
-        <v>2679</v>
+        <v>2722</v>
       </c>
       <c r="B265" t="s">
         <v>22</v>
       </c>
       <c r="C265" t="s">
-        <v>2892</v>
+        <v>2935</v>
       </c>
       <c r="D265" t="s">
         <v>2105</v>
@@ -23164,13 +24035,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" t="s">
-        <v>2680</v>
+        <v>2723</v>
       </c>
       <c r="B266" t="s">
         <v>27</v>
       </c>
       <c r="C266" t="s">
-        <v>2893</v>
+        <v>2936</v>
       </c>
       <c r="D266" t="s">
         <v>332</v>
@@ -23178,13 +24049,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" t="s">
-        <v>2681</v>
+        <v>2724</v>
       </c>
       <c r="B267" t="s">
         <v>27</v>
       </c>
       <c r="C267" t="s">
-        <v>2894</v>
+        <v>2937</v>
       </c>
       <c r="D267" t="s">
         <v>332</v>
@@ -23192,13 +24063,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" t="s">
-        <v>2682</v>
+        <v>2725</v>
       </c>
       <c r="B268" t="s">
         <v>27</v>
       </c>
       <c r="C268" t="s">
-        <v>2785</v>
+        <v>2828</v>
       </c>
       <c r="D268" t="s">
         <v>2105</v>
@@ -23206,13 +24077,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" t="s">
-        <v>2683</v>
+        <v>2726</v>
       </c>
       <c r="B269" t="s">
         <v>27</v>
       </c>
       <c r="C269" t="s">
-        <v>2895</v>
+        <v>2938</v>
       </c>
       <c r="D269" t="s">
         <v>332</v>
@@ -23220,13 +24091,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" t="s">
-        <v>2684</v>
+        <v>2727</v>
       </c>
       <c r="B270" t="s">
         <v>27</v>
       </c>
       <c r="C270" t="s">
-        <v>2789</v>
+        <v>2832</v>
       </c>
       <c r="D270" t="s">
         <v>2105</v>
@@ -23234,13 +24105,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" t="s">
-        <v>2685</v>
+        <v>2728</v>
       </c>
       <c r="B271" t="s">
         <v>27</v>
       </c>
       <c r="C271" t="s">
-        <v>2896</v>
+        <v>2939</v>
       </c>
       <c r="D271" t="s">
         <v>332</v>
@@ -23248,13 +24119,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" t="s">
-        <v>2686</v>
+        <v>2729</v>
       </c>
       <c r="B272" t="s">
         <v>27</v>
       </c>
       <c r="C272" t="s">
-        <v>2768</v>
+        <v>2811</v>
       </c>
       <c r="D272" t="s">
         <v>2105</v>
@@ -23262,13 +24133,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" t="s">
-        <v>2687</v>
+        <v>2730</v>
       </c>
       <c r="B273" t="s">
         <v>27</v>
       </c>
       <c r="C273" t="s">
-        <v>2897</v>
+        <v>2940</v>
       </c>
       <c r="D273" t="s">
         <v>332</v>
@@ -23276,13 +24147,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" t="s">
-        <v>2688</v>
+        <v>2731</v>
       </c>
       <c r="B274" t="s">
         <v>27</v>
       </c>
       <c r="C274" t="s">
-        <v>2776</v>
+        <v>2819</v>
       </c>
       <c r="D274" t="s">
         <v>2105</v>
@@ -23290,13 +24161,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" t="s">
-        <v>2689</v>
+        <v>2732</v>
       </c>
       <c r="B275" t="s">
         <v>27</v>
       </c>
       <c r="C275" t="s">
-        <v>2898</v>
+        <v>2941</v>
       </c>
       <c r="D275" t="s">
         <v>332</v>
@@ -23304,13 +24175,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" t="s">
-        <v>2690</v>
+        <v>2733</v>
       </c>
       <c r="B276" t="s">
         <v>27</v>
       </c>
       <c r="C276" t="s">
-        <v>2756</v>
+        <v>2799</v>
       </c>
       <c r="D276" t="s">
         <v>2105</v>
@@ -23318,13 +24189,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" t="s">
-        <v>2691</v>
+        <v>2734</v>
       </c>
       <c r="B277" t="s">
         <v>27</v>
       </c>
       <c r="C277" t="s">
-        <v>2899</v>
+        <v>2942</v>
       </c>
       <c r="D277" t="s">
         <v>332</v>
@@ -23332,13 +24203,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" t="s">
-        <v>2692</v>
+        <v>2735</v>
       </c>
       <c r="B278" t="s">
         <v>27</v>
       </c>
       <c r="C278" t="s">
-        <v>2761</v>
+        <v>2804</v>
       </c>
       <c r="D278" t="s">
         <v>2105</v>
@@ -23346,13 +24217,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B279" t="s">
         <v>27</v>
       </c>
       <c r="C279" t="s">
-        <v>2900</v>
+        <v>2943</v>
       </c>
       <c r="D279" t="s">
         <v>332</v>
@@ -23360,13 +24231,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B280" t="s">
         <v>23</v>
       </c>
       <c r="C280" t="s">
-        <v>2901</v>
+        <v>2944</v>
       </c>
       <c r="D280" t="s">
         <v>332</v>
@@ -23374,13 +24245,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B281" t="s">
         <v>24</v>
       </c>
       <c r="C281" t="s">
-        <v>2901</v>
+        <v>2944</v>
       </c>
       <c r="D281" t="s">
         <v>332</v>
@@ -23388,13 +24259,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B282" t="s">
         <v>22</v>
       </c>
       <c r="C282" t="s">
-        <v>2902</v>
+        <v>2945</v>
       </c>
       <c r="D282" t="s">
         <v>332</v>
@@ -23402,13 +24273,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B283" t="s">
         <v>25</v>
       </c>
       <c r="C283" t="s">
-        <v>2900</v>
+        <v>2943</v>
       </c>
       <c r="D283" t="s">
         <v>332</v>
@@ -23416,13 +24287,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" t="s">
-        <v>2693</v>
+        <v>2736</v>
       </c>
       <c r="B284" t="s">
         <v>1600</v>
       </c>
       <c r="C284" t="s">
-        <v>2903</v>
+        <v>2946</v>
       </c>
       <c r="D284" t="s">
         <v>332</v>
@@ -23430,13 +24301,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" t="s">
-        <v>2694</v>
+        <v>2737</v>
       </c>
       <c r="B285" t="s">
         <v>27</v>
       </c>
       <c r="C285" t="s">
-        <v>2904</v>
+        <v>2947</v>
       </c>
       <c r="D285" t="s">
         <v>332</v>
@@ -23444,13 +24315,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" t="s">
-        <v>2695</v>
+        <v>2738</v>
       </c>
       <c r="B286" t="s">
         <v>27</v>
       </c>
       <c r="C286" t="s">
-        <v>2756</v>
+        <v>2799</v>
       </c>
       <c r="D286" t="s">
         <v>2105</v>
@@ -23458,13 +24329,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" t="s">
-        <v>2696</v>
+        <v>2739</v>
       </c>
       <c r="B287" t="s">
         <v>27</v>
       </c>
       <c r="C287" t="s">
-        <v>2905</v>
+        <v>2948</v>
       </c>
       <c r="D287" t="s">
         <v>332</v>
@@ -23472,13 +24343,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" t="s">
-        <v>2697</v>
+        <v>2740</v>
       </c>
       <c r="B288" t="s">
         <v>27</v>
       </c>
       <c r="C288" t="s">
-        <v>2761</v>
+        <v>2804</v>
       </c>
       <c r="D288" t="s">
         <v>2105</v>
@@ -23486,13 +24357,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" t="s">
-        <v>2698</v>
+        <v>2741</v>
       </c>
       <c r="B289" t="s">
         <v>27</v>
       </c>
       <c r="C289" t="s">
-        <v>2906</v>
+        <v>2949</v>
       </c>
       <c r="D289" t="s">
         <v>332</v>
@@ -23500,13 +24371,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" t="s">
-        <v>2699</v>
+        <v>2742</v>
       </c>
       <c r="B290" t="s">
         <v>27</v>
       </c>
       <c r="C290" t="s">
-        <v>2768</v>
+        <v>2811</v>
       </c>
       <c r="D290" t="s">
         <v>2105</v>
@@ -23514,13 +24385,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" t="s">
-        <v>2700</v>
+        <v>2743</v>
       </c>
       <c r="B291" t="s">
         <v>27</v>
       </c>
       <c r="C291" t="s">
-        <v>2907</v>
+        <v>2950</v>
       </c>
       <c r="D291" t="s">
         <v>332</v>
@@ -23528,13 +24399,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" t="s">
-        <v>2701</v>
+        <v>2744</v>
       </c>
       <c r="B292" t="s">
         <v>27</v>
       </c>
       <c r="C292" t="s">
-        <v>2776</v>
+        <v>2819</v>
       </c>
       <c r="D292" t="s">
         <v>2105</v>
@@ -23542,13 +24413,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" t="s">
-        <v>2702</v>
+        <v>2745</v>
       </c>
       <c r="B293" t="s">
         <v>27</v>
       </c>
       <c r="C293" t="s">
-        <v>2908</v>
+        <v>2951</v>
       </c>
       <c r="D293" t="s">
         <v>332</v>
@@ -23556,13 +24427,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" t="s">
-        <v>2703</v>
+        <v>2746</v>
       </c>
       <c r="B294" t="s">
         <v>27</v>
       </c>
       <c r="C294" t="s">
-        <v>2785</v>
+        <v>2828</v>
       </c>
       <c r="D294" t="s">
         <v>2105</v>
@@ -23570,13 +24441,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" t="s">
-        <v>2704</v>
+        <v>2747</v>
       </c>
       <c r="B295" t="s">
         <v>27</v>
       </c>
       <c r="C295" t="s">
-        <v>2909</v>
+        <v>2952</v>
       </c>
       <c r="D295" t="s">
         <v>332</v>
@@ -23584,13 +24455,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" t="s">
-        <v>2705</v>
+        <v>2748</v>
       </c>
       <c r="B296" t="s">
         <v>27</v>
       </c>
       <c r="C296" t="s">
-        <v>2789</v>
+        <v>2832</v>
       </c>
       <c r="D296" t="s">
         <v>2105</v>
@@ -23622,13 +24493,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>2910</v>
+        <v>2953</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>2922</v>
+        <v>2965</v>
       </c>
       <c r="D2" t="s">
         <v>332</v>
@@ -23636,13 +24507,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>2910</v>
+        <v>2953</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>2922</v>
+        <v>2965</v>
       </c>
       <c r="D3" t="s">
         <v>332</v>
@@ -23650,13 +24521,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2911</v>
+        <v>2954</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>2923</v>
+        <v>2966</v>
       </c>
       <c r="D4" t="s">
         <v>333</v>
@@ -23664,13 +24535,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>2911</v>
+        <v>2954</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>2923</v>
+        <v>2966</v>
       </c>
       <c r="D5" t="s">
         <v>333</v>
@@ -23678,13 +24549,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>2912</v>
+        <v>2955</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>2924</v>
+        <v>2967</v>
       </c>
       <c r="D6" t="s">
         <v>332</v>
@@ -23692,13 +24563,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>2912</v>
+        <v>2955</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>2924</v>
+        <v>2967</v>
       </c>
       <c r="D7" t="s">
         <v>332</v>
@@ -23706,7 +24577,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>2913</v>
+        <v>2956</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
@@ -23720,7 +24591,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>2913</v>
+        <v>2956</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
@@ -23734,13 +24605,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>2914</v>
+        <v>2957</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>2925</v>
+        <v>2968</v>
       </c>
       <c r="D10" t="s">
         <v>332</v>
@@ -23748,13 +24619,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>2914</v>
+        <v>2957</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>2925</v>
+        <v>2968</v>
       </c>
       <c r="D11" t="s">
         <v>332</v>
@@ -23762,13 +24633,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>2914</v>
+        <v>2957</v>
       </c>
       <c r="B12" t="s">
         <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>2926</v>
+        <v>2969</v>
       </c>
       <c r="D12" t="s">
         <v>332</v>
@@ -23776,13 +24647,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>2915</v>
+        <v>2958</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>2927</v>
+        <v>2970</v>
       </c>
       <c r="D13" t="s">
         <v>333</v>
@@ -23790,13 +24661,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>2915</v>
+        <v>2958</v>
       </c>
       <c r="B14" t="s">
         <v>24</v>
       </c>
       <c r="C14" t="s">
-        <v>2927</v>
+        <v>2970</v>
       </c>
       <c r="D14" t="s">
         <v>333</v>
@@ -23804,13 +24675,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>2915</v>
+        <v>2958</v>
       </c>
       <c r="B15" t="s">
         <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>2928</v>
+        <v>2971</v>
       </c>
       <c r="D15" t="s">
         <v>333</v>
@@ -23818,13 +24689,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>2916</v>
+        <v>2959</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>2929</v>
+        <v>2972</v>
       </c>
       <c r="D16" t="s">
         <v>332</v>
@@ -23832,13 +24703,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>2916</v>
+        <v>2959</v>
       </c>
       <c r="B17" t="s">
         <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>2929</v>
+        <v>2972</v>
       </c>
       <c r="D17" t="s">
         <v>332</v>
@@ -23846,13 +24717,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>2916</v>
+        <v>2959</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>2930</v>
+        <v>2973</v>
       </c>
       <c r="D18" t="s">
         <v>332</v>
@@ -23860,13 +24731,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>2916</v>
+        <v>2959</v>
       </c>
       <c r="B19" t="s">
         <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>2931</v>
+        <v>2974</v>
       </c>
       <c r="D19" t="s">
         <v>332</v>
@@ -23874,7 +24745,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>2917</v>
+        <v>2960</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -23888,7 +24759,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>2917</v>
+        <v>2960</v>
       </c>
       <c r="B21" t="s">
         <v>24</v>
@@ -23902,13 +24773,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>2917</v>
+        <v>2960</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>2932</v>
+        <v>2975</v>
       </c>
       <c r="D22" t="s">
         <v>333</v>
@@ -23916,13 +24787,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>2917</v>
+        <v>2960</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23" t="s">
-        <v>2933</v>
+        <v>2976</v>
       </c>
       <c r="D23" t="s">
         <v>333</v>
@@ -23930,13 +24801,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>2918</v>
+        <v>2961</v>
       </c>
       <c r="B24" t="s">
         <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>2934</v>
+        <v>2977</v>
       </c>
       <c r="D24" t="s">
         <v>332</v>
@@ -23944,13 +24815,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>2918</v>
+        <v>2961</v>
       </c>
       <c r="B25" t="s">
         <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>2934</v>
+        <v>2977</v>
       </c>
       <c r="D25" t="s">
         <v>332</v>
@@ -23958,13 +24829,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>2919</v>
+        <v>2962</v>
       </c>
       <c r="B26" t="s">
         <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>2935</v>
+        <v>2978</v>
       </c>
       <c r="D26" t="s">
         <v>333</v>
@@ -23972,13 +24843,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>2919</v>
+        <v>2962</v>
       </c>
       <c r="B27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>2935</v>
+        <v>2978</v>
       </c>
       <c r="D27" t="s">
         <v>333</v>
@@ -23986,13 +24857,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>2920</v>
+        <v>2963</v>
       </c>
       <c r="B28" t="s">
         <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>2936</v>
+        <v>2979</v>
       </c>
       <c r="D28" t="s">
         <v>332</v>
@@ -24000,13 +24871,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>2920</v>
+        <v>2963</v>
       </c>
       <c r="B29" t="s">
         <v>24</v>
       </c>
       <c r="C29" t="s">
-        <v>2936</v>
+        <v>2979</v>
       </c>
       <c r="D29" t="s">
         <v>332</v>
@@ -24014,7 +24885,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>2921</v>
+        <v>2964</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
@@ -24028,7 +24899,7 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>2921</v>
+        <v>2964</v>
       </c>
       <c r="B31" t="s">
         <v>24</v>
